--- a/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.xlsx
+++ b/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="897">
   <si>
-    <t>Run date/time: 2026-07-03 14:35:48</t>
+    <t>Run date/time: 2026-07-06 20:48:37</t>
   </si>
   <si>
     <t>Code Base Details</t>
@@ -124,7 +124,7 @@
     <t>-d</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql</t>
   </si>
   <si>
     <t>-e</t>
@@ -133,13 +133,13 @@
     <t>-j</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.json</t>
+    <t>D:\autovista\output_lakebridge\reports\lakebridge_report_MS_SQL_Server.json</t>
   </si>
   <si>
     <t>-r</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.xlsx</t>
+    <t>D:\autovista\output_lakebridge\reports\lakebridge_report_MS_SQL_Server.xlsx</t>
   </si>
   <si>
     <t>-t</t>
@@ -151,7 +151,7 @@
     <t>Analyzer run duration:</t>
   </si>
   <si>
-    <t>0h, 0m, 1s</t>
+    <t>0h, 0m, 4s</t>
   </si>
   <si>
     <t>Program Name</t>
@@ -193,7 +193,7 @@
     <t>sql_scalar_function__dbo.ufnGetAccountingEndDate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingEndDate.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingEndDate.sql</t>
   </si>
   <si>
     <t>YES</t>
@@ -220,7 +220,7 @@
     <t>sql_scalar_function__dbo.ufnGetAccountingStartDate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingStartDate.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingStartDate.sql</t>
   </si>
   <si>
     <t>BAF6458A7E562903BA94D801522005A0</t>
@@ -232,7 +232,7 @@
     <t>sql_scalar_function__dbo.ufnGetDocumentStatusText.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetDocumentStatusText.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetDocumentStatusText.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -250,7 +250,7 @@
     <t>sql_scalar_function__dbo.ufnGetProductDealerPrice.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductDealerPrice.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductDealerPrice.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,SELECT_VAR_ASSIGNMENT,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -268,7 +268,7 @@
     <t>sql_scalar_function__dbo.ufnGetProductListPrice.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductListPrice.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductListPrice.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,SELECT_VAR_ASSIGNMENT,UNKNOWN,VAR_DECLARE</t>
@@ -286,7 +286,7 @@
     <t>sql_scalar_function__dbo.ufnGetProductStandardCost.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductStandardCost.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductStandardCost.sql</t>
   </si>
   <si>
     <t>8F43C9F49781DB147EE70E52AF3E8C18</t>
@@ -298,7 +298,7 @@
     <t>sql_scalar_function__dbo.ufnGetPurchaseOrderStatusText.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetPurchaseOrderStatusText.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetPurchaseOrderStatusText.sql</t>
   </si>
   <si>
     <t>65A240477CA9503CB1F2D199C2B26A96</t>
@@ -310,7 +310,7 @@
     <t>sql_scalar_function__dbo.ufnGetSalesOrderStatusText.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetSalesOrderStatusText.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetSalesOrderStatusText.sql</t>
   </si>
   <si>
     <t>0B4FB00504955E9B32739F20AE320DF0</t>
@@ -322,7 +322,7 @@
     <t>sql_scalar_function__dbo.ufnGetStock.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetStock.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetStock.sql</t>
   </si>
   <si>
     <t>IF_START,PROGRAM_DECLARATION,SELECT_VAR_ASSIGNMENT,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -340,7 +340,7 @@
     <t>sql_scalar_function__dbo.ufnLeadingZeros.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnLeadingZeros.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnLeadingZeros.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -358,7 +358,7 @@
     <t>sql_stored_procedure__HumanResources.uspUpdateEmployeeHireInfo.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeHireInfo.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeHireInfo.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,DYNAMIC_SQL,IF_START,INSERT_INTO,UNKNOWN,UPDATE</t>
@@ -376,7 +376,7 @@
     <t>sql_stored_procedure__HumanResources.uspUpdateEmployeeLogin.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeLogin.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeLogin.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,DYNAMIC_SQL,UNKNOWN,UPDATE</t>
@@ -394,7 +394,7 @@
     <t>sql_stored_procedure__HumanResources.uspUpdateEmployeePersonalInfo.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeePersonalInfo.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeePersonalInfo.sql</t>
   </si>
   <si>
     <t>1150510C0F295A53ABB21132050E1842</t>
@@ -406,7 +406,7 @@
     <t>sql_stored_procedure__dbo.uspGetBillOfMaterials.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetBillOfMaterials.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetBillOfMaterials.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,WITH</t>
@@ -424,7 +424,7 @@
     <t>sql_stored_procedure__dbo.uspGetEmployeeManagers.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetEmployeeManagers.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetEmployeeManagers.sql</t>
   </si>
   <si>
     <t>2D5E9F29ED5FDBF0970D8E1DEB7EF7EF</t>
@@ -436,7 +436,7 @@
     <t>sql_stored_procedure__dbo.uspGetManagerEmployees.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetManagerEmployees.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetManagerEmployees.sql</t>
   </si>
   <si>
     <t>8B11ABC3F784D412FED8C567819B2188</t>
@@ -448,7 +448,7 @@
     <t>sql_stored_procedure__dbo.uspGetWhereUsedProductID.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetWhereUsedProductID.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetWhereUsedProductID.sql</t>
   </si>
   <si>
     <t>8FFD5EAF979D3F33C7B8447189E5CC10</t>
@@ -460,7 +460,7 @@
     <t>sql_stored_procedure__dbo.uspLogError.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspLogError.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspLogError.sql</t>
   </si>
   <si>
     <t>MEDIUM</t>
@@ -481,7 +481,7 @@
     <t>sql_stored_procedure__dbo.uspPrintError.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspPrintError.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspPrintError.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,UNKNOWN</t>
@@ -499,7 +499,7 @@
     <t>sql_stored_procedure__dbo.uspSearchCandidateResumes.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspSearchCandidateResumes.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspSearchCandidateResumes.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,DYNAMIC_SQL,ELSE_IF,IF_START,SELECT_VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -517,7 +517,7 @@
     <t>sql_table_valued_function__dbo.ufnGetContactInformation.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_table_valued_function__dbo.ufnGetContactInformation.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_table_valued_function__dbo.ufnGetContactInformation.sql</t>
   </si>
   <si>
     <t>IF_START,INSERT_INTO,PROGRAM_DECLARATION,UNKNOWN</t>
@@ -535,7 +535,7 @@
     <t>sql_trigger__HumanResources.dEmployee.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__HumanResources.dEmployee.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__HumanResources.dEmployee.sql</t>
   </si>
   <si>
     <t>DELETE,FOR,IF_START,SET,TRIGGER,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -553,7 +553,7 @@
     <t>sql_trigger__Person.iuPerson.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Person.iuPerson.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Person.iuPerson.sql</t>
   </si>
   <si>
     <t>FOR,IF_START,INSERT,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -571,7 +571,7 @@
     <t>sql_trigger__Production.iWorkOrder.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Production.iWorkOrder.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Production.iWorkOrder.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,INSERT,INSERT_INTO,SET,TRIGGER,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -589,7 +589,7 @@
     <t>sql_trigger__Production.uWorkOrder.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Production.uWorkOrder.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Production.uWorkOrder.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,INSERT_INTO,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -607,7 +607,7 @@
     <t>sql_trigger__Purchasing.dVendor.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.dVendor.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.dVendor.sql</t>
   </si>
   <si>
     <t>DELETE,DYNAMIC_SQL,FOR,IF_START,SELECT_VAR_ASSIGNMENT,SET,TRIGGER,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -625,7 +625,7 @@
     <t>sql_trigger__Purchasing.iPurchaseOrderDetail.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.iPurchaseOrderDetail.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.iPurchaseOrderDetail.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,INSERT,INSERT_INTO,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -643,7 +643,7 @@
     <t>sql_trigger__Purchasing.uPurchaseOrderDetail.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderDetail.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderDetail.sql</t>
   </si>
   <si>
     <t>Total Statement count: 22, Conventional Statement count: 14, Simple Statement count: 8, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -658,7 +658,7 @@
     <t>sql_trigger__Purchasing.uPurchaseOrderHeader.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderHeader.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderHeader.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -676,7 +676,7 @@
     <t>sql_trigger__Sales.iduSalesOrderDetail.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Sales.iduSalesOrderDetail.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Sales.iduSalesOrderDetail.sql</t>
   </si>
   <si>
     <t>DELETE,DYNAMIC_SQL,IF_START,INSERT_INTO,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -694,7 +694,7 @@
     <t>sql_trigger__Sales.uSalesOrderHeader.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Sales.uSalesOrderHeader.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Sales.uSalesOrderHeader.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,FOR,IF_START,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -712,7 +712,7 @@
     <t>table__HumanResources.Department.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.Department.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.Department.sql</t>
   </si>
   <si>
     <t>TABLE_DDL</t>
@@ -730,7 +730,7 @@
     <t>table__HumanResources.Employee.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.Employee.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.Employee.sql</t>
   </si>
   <si>
     <t>A09D1501EFF964FC7F93C28EF51C360A</t>
@@ -742,7 +742,7 @@
     <t>table__HumanResources.EmployeeDepartmentHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.EmployeeDepartmentHistory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.EmployeeDepartmentHistory.sql</t>
   </si>
   <si>
     <t>9228830EC44A62F7A7D2C8F41850032F</t>
@@ -754,7 +754,7 @@
     <t>table__HumanResources.EmployeePayHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.EmployeePayHistory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.EmployeePayHistory.sql</t>
   </si>
   <si>
     <t>42D4CA98D5026067D7084C89A9AF12B6</t>
@@ -766,7 +766,7 @@
     <t>table__HumanResources.JobCandidate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.JobCandidate.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.JobCandidate.sql</t>
   </si>
   <si>
     <t>D678671C1A1D596D2DFB28AF39E3DBBC</t>
@@ -778,7 +778,7 @@
     <t>table__HumanResources.Shift.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.Shift.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.Shift.sql</t>
   </si>
   <si>
     <t>0839B989DA5FCAF2B2737EBC540D47FA</t>
@@ -790,7 +790,7 @@
     <t>table__Person.Address.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.Address.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.Address.sql</t>
   </si>
   <si>
     <t>485B09A2BAF22C3CD474D91BB496DDA3</t>
@@ -802,7 +802,7 @@
     <t>table__Person.AddressType.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.AddressType.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.AddressType.sql</t>
   </si>
   <si>
     <t>08B4363009B611557F05C437003C683F</t>
@@ -814,7 +814,7 @@
     <t>table__Person.BusinessEntity.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.BusinessEntity.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.BusinessEntity.sql</t>
   </si>
   <si>
     <t>9A22940EBB8A151E20E568F9C55DF1AE</t>
@@ -826,7 +826,7 @@
     <t>table__Person.BusinessEntityAddress.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.BusinessEntityAddress.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.BusinessEntityAddress.sql</t>
   </si>
   <si>
     <t>526B5BBA957622BBC2F5259A809EACD6</t>
@@ -838,7 +838,7 @@
     <t>table__Person.BusinessEntityContact.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.BusinessEntityContact.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.BusinessEntityContact.sql</t>
   </si>
   <si>
     <t>5B8957D0AC73C90AB40E85FBA5364190</t>
@@ -850,7 +850,7 @@
     <t>table__Person.ContactType.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.ContactType.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.ContactType.sql</t>
   </si>
   <si>
     <t>5E5B91699E103EB7CFF0FCB8160603BA</t>
@@ -862,7 +862,7 @@
     <t>table__Person.CountryRegion.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.CountryRegion.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.CountryRegion.sql</t>
   </si>
   <si>
     <t>5BB96BCDDBBDEBADF135B661C19B350B</t>
@@ -874,7 +874,7 @@
     <t>table__Person.EmailAddress.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.EmailAddress.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.EmailAddress.sql</t>
   </si>
   <si>
     <t>4B896C74F29899543C11EC768F32409B</t>
@@ -886,7 +886,7 @@
     <t>table__Person.Password.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.Password.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.Password.sql</t>
   </si>
   <si>
     <t>2E2A0FE95B210391BE42F9071EDE48BE</t>
@@ -898,7 +898,7 @@
     <t>table__Person.Person.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.Person.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.Person.sql</t>
   </si>
   <si>
     <t>CEA71116F62DA77C29D73CA35A022768</t>
@@ -910,7 +910,7 @@
     <t>table__Person.PersonPhone.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.PersonPhone.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.PersonPhone.sql</t>
   </si>
   <si>
     <t>60F9C8F4F9550E33504D90B5A74C70CC</t>
@@ -922,7 +922,7 @@
     <t>table__Person.PhoneNumberType.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.PhoneNumberType.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.PhoneNumberType.sql</t>
   </si>
   <si>
     <t>DBA25BAC265188C8967469364B9CE7FA</t>
@@ -934,7 +934,7 @@
     <t>table__Person.StateProvince.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.StateProvince.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.StateProvince.sql</t>
   </si>
   <si>
     <t>57D5CF4EEBA86A111B55FEEB79FFEDEC</t>
@@ -946,7 +946,7 @@
     <t>table__Production.BillOfMaterials.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.BillOfMaterials.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.BillOfMaterials.sql</t>
   </si>
   <si>
     <t>B41188C3DFF17B6A689AC8102D2BC1A6</t>
@@ -958,7 +958,7 @@
     <t>table__Production.Culture.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Culture.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.Culture.sql</t>
   </si>
   <si>
     <t>1C130C6BDF76C57176E59BF82D6F45E3</t>
@@ -970,7 +970,7 @@
     <t>table__Production.Document.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Document.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.Document.sql</t>
   </si>
   <si>
     <t>87223ADE7453748D59A4D77AB9161990</t>
@@ -982,7 +982,7 @@
     <t>table__Production.Illustration.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Illustration.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.Illustration.sql</t>
   </si>
   <si>
     <t>CDF25A85A06B21D4F894436430687C5F</t>
@@ -994,7 +994,7 @@
     <t>table__Production.Location.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Location.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.Location.sql</t>
   </si>
   <si>
     <t>0545BD908EB198803B1693015A3CE02B</t>
@@ -1006,7 +1006,7 @@
     <t>table__Production.Product.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Product.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.Product.sql</t>
   </si>
   <si>
     <t>E1A2837A7C58D9A163BF2F99F4BA918D</t>
@@ -1018,7 +1018,7 @@
     <t>table__Production.ProductCategory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductCategory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductCategory.sql</t>
   </si>
   <si>
     <t>3E35F2E89EEF417646F4CB4FBC17592A</t>
@@ -1030,7 +1030,7 @@
     <t>table__Production.ProductCostHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductCostHistory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductCostHistory.sql</t>
   </si>
   <si>
     <t>4261C77ACD861463971A72947ADEF0EB</t>
@@ -1042,7 +1042,7 @@
     <t>table__Production.ProductDescription.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductDescription.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductDescription.sql</t>
   </si>
   <si>
     <t>0A97183ACE800325530795C427B00F6A</t>
@@ -1054,7 +1054,7 @@
     <t>table__Production.ProductDocument.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductDocument.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductDocument.sql</t>
   </si>
   <si>
     <t>0398181199286BC96BFF033204F24025</t>
@@ -1066,7 +1066,7 @@
     <t>table__Production.ProductInventory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductInventory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductInventory.sql</t>
   </si>
   <si>
     <t>46D249B5A8EFF075AB470002B5C668B6</t>
@@ -1078,7 +1078,7 @@
     <t>table__Production.ProductListPriceHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductListPriceHistory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductListPriceHistory.sql</t>
   </si>
   <si>
     <t>23E2E2CA129E8DD01419C2370395097F</t>
@@ -1090,7 +1090,7 @@
     <t>table__Production.ProductModel.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductModel.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductModel.sql</t>
   </si>
   <si>
     <t>D05E0BF2770E989EF1DE2CA52468EDF5</t>
@@ -1102,7 +1102,7 @@
     <t>table__Production.ProductModelIllustration.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductModelIllustration.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductModelIllustration.sql</t>
   </si>
   <si>
     <t>BD221B96177793334973969A64B4BEBC</t>
@@ -1114,7 +1114,7 @@
     <t>table__Production.ProductModelProductDescriptionCulture.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductModelProductDescriptionCulture.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductModelProductDescriptionCulture.sql</t>
   </si>
   <si>
     <t>F35D2447ADCD0DA859EAF287626D974A</t>
@@ -1126,7 +1126,7 @@
     <t>table__Production.ProductPhoto.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductPhoto.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductPhoto.sql</t>
   </si>
   <si>
     <t>03C219754DA19CB82B6FD396EB6F28C5</t>
@@ -1138,7 +1138,7 @@
     <t>table__Production.ProductProductPhoto.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductProductPhoto.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductProductPhoto.sql</t>
   </si>
   <si>
     <t>876476D3B77644342259555E0A10E5F1</t>
@@ -1150,7 +1150,7 @@
     <t>table__Production.ProductReview.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductReview.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductReview.sql</t>
   </si>
   <si>
     <t>7C377BBF6513688CA880F9F9D0F1D76E</t>
@@ -1162,7 +1162,7 @@
     <t>table__Production.ProductSubcategory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductSubcategory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductSubcategory.sql</t>
   </si>
   <si>
     <t>EA8F0B633FC9352809AB4AB26BDA306C</t>
@@ -1174,7 +1174,7 @@
     <t>table__Production.ScrapReason.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ScrapReason.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ScrapReason.sql</t>
   </si>
   <si>
     <t>C2AD160F44D5EDD63F11596C05CCBA51</t>
@@ -1186,7 +1186,7 @@
     <t>table__Production.TransactionHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.TransactionHistory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.TransactionHistory.sql</t>
   </si>
   <si>
     <t>13719707E5535F85CF798C7F5DAF155B</t>
@@ -1198,7 +1198,7 @@
     <t>table__Production.TransactionHistoryArchive.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.TransactionHistoryArchive.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.TransactionHistoryArchive.sql</t>
   </si>
   <si>
     <t>544F70FCAE619680F6C9951951608CDD</t>
@@ -1210,7 +1210,7 @@
     <t>table__Production.UnitMeasure.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.UnitMeasure.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.UnitMeasure.sql</t>
   </si>
   <si>
     <t>E24E10E408A06B9F5C59D83FF0CA225D</t>
@@ -1222,7 +1222,7 @@
     <t>table__Production.WorkOrder.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.WorkOrder.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.WorkOrder.sql</t>
   </si>
   <si>
     <t>41344D16748C45BF0868FF364D49878E</t>
@@ -1234,7 +1234,7 @@
     <t>table__Production.WorkOrderRouting.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.WorkOrderRouting.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.WorkOrderRouting.sql</t>
   </si>
   <si>
     <t>B08836F89C3812FCAD7848493AC6C222</t>
@@ -1246,7 +1246,7 @@
     <t>table__Purchasing.ProductVendor.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.ProductVendor.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Purchasing.ProductVendor.sql</t>
   </si>
   <si>
     <t>9E2E628A6B381784205541577DB178F3</t>
@@ -1258,7 +1258,7 @@
     <t>table__Purchasing.PurchaseOrderDetail.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderDetail.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderDetail.sql</t>
   </si>
   <si>
     <t>36588C425A912EBB636171FA624E54CA</t>
@@ -1270,7 +1270,7 @@
     <t>table__Purchasing.PurchaseOrderHeader.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderHeader.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderHeader.sql</t>
   </si>
   <si>
     <t>B5FF0036905B4D6641D97D3DD82A9125</t>
@@ -1282,7 +1282,7 @@
     <t>table__Purchasing.ShipMethod.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.ShipMethod.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Purchasing.ShipMethod.sql</t>
   </si>
   <si>
     <t>53C0287AFAFB7FACD5130ABA4F5A63DC</t>
@@ -1294,7 +1294,7 @@
     <t>table__Purchasing.Vendor.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.Vendor.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Purchasing.Vendor.sql</t>
   </si>
   <si>
     <t>0C3481C46FCF8839B53FA1C7AF77D661</t>
@@ -1306,7 +1306,7 @@
     <t>table__Sales.CountryRegionCurrency.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.CountryRegionCurrency.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.CountryRegionCurrency.sql</t>
   </si>
   <si>
     <t>CB23C961AD6C0967CBCE83F7B7D4252F</t>
@@ -1318,7 +1318,7 @@
     <t>table__Sales.CreditCard.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.CreditCard.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.CreditCard.sql</t>
   </si>
   <si>
     <t>86C19DBC9CB4B9BE848969BB70852DB6</t>
@@ -1330,7 +1330,7 @@
     <t>table__Sales.Currency.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.Currency.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.Currency.sql</t>
   </si>
   <si>
     <t>49DA4C335C4301DABE0D4AC5791CA07F</t>
@@ -1342,7 +1342,7 @@
     <t>table__Sales.CurrencyRate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.CurrencyRate.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.CurrencyRate.sql</t>
   </si>
   <si>
     <t>A58B28FFBB12FBB0CA0E3766DF35B07E</t>
@@ -1354,7 +1354,7 @@
     <t>table__Sales.Customer.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.Customer.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.Customer.sql</t>
   </si>
   <si>
     <t>E6FC49B6E1B25B07E04DF33CE45F4399</t>
@@ -1366,7 +1366,7 @@
     <t>table__Sales.PersonCreditCard.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.PersonCreditCard.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.PersonCreditCard.sql</t>
   </si>
   <si>
     <t>A241FDEF93235427CF91A5507973980F</t>
@@ -1378,7 +1378,7 @@
     <t>table__Sales.SalesOrderDetail.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesOrderDetail.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesOrderDetail.sql</t>
   </si>
   <si>
     <t>E1099694C073E244D0B1732BFE40C2AB</t>
@@ -1390,7 +1390,7 @@
     <t>table__Sales.SalesOrderHeader.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeader.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeader.sql</t>
   </si>
   <si>
     <t>7354A80681291374434F107181B3B86A</t>
@@ -1402,7 +1402,7 @@
     <t>table__Sales.SalesOrderHeaderSalesReason.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeaderSalesReason.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeaderSalesReason.sql</t>
   </si>
   <si>
     <t>7A24418F81E279698B5FF138D4BFB170</t>
@@ -1414,7 +1414,7 @@
     <t>table__Sales.SalesPerson.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesPerson.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesPerson.sql</t>
   </si>
   <si>
     <t>49179896BB64CA95587BABDD2A7E43D4</t>
@@ -1426,7 +1426,7 @@
     <t>table__Sales.SalesPersonQuotaHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesPersonQuotaHistory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesPersonQuotaHistory.sql</t>
   </si>
   <si>
     <t>FDEE90B15CAD405E463BFF80FD75EF34</t>
@@ -1438,7 +1438,7 @@
     <t>table__Sales.SalesReason.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesReason.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesReason.sql</t>
   </si>
   <si>
     <t>47485D008572AEEFECB84EE3E0F1DE6E</t>
@@ -1450,7 +1450,7 @@
     <t>table__Sales.SalesTaxRate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesTaxRate.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesTaxRate.sql</t>
   </si>
   <si>
     <t>32719803958AC6D18D90AA966A22B082</t>
@@ -1462,7 +1462,7 @@
     <t>table__Sales.SalesTerritory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesTerritory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesTerritory.sql</t>
   </si>
   <si>
     <t>B790E7EFC56E9AC828FFDE5038CFADB6</t>
@@ -1474,7 +1474,7 @@
     <t>table__Sales.SalesTerritoryHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesTerritoryHistory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesTerritoryHistory.sql</t>
   </si>
   <si>
     <t>1244394A085CB4B94173FDD051942941</t>
@@ -1486,7 +1486,7 @@
     <t>table__Sales.ShoppingCartItem.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.ShoppingCartItem.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.ShoppingCartItem.sql</t>
   </si>
   <si>
     <t>9EE4E094750CB2905440942505351ADA</t>
@@ -1498,7 +1498,7 @@
     <t>table__Sales.SpecialOffer.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SpecialOffer.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SpecialOffer.sql</t>
   </si>
   <si>
     <t>F34B35578D75C869E165D90095D3E093</t>
@@ -1510,7 +1510,7 @@
     <t>table__Sales.SpecialOfferProduct.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SpecialOfferProduct.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SpecialOfferProduct.sql</t>
   </si>
   <si>
     <t>90353DD5FEA1EE6BC0D43B195EE9727F</t>
@@ -1522,7 +1522,7 @@
     <t>table__Sales.Store.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.Store.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.Store.sql</t>
   </si>
   <si>
     <t>73C4AAD5EC0DEF9534BCA7A958692CEC</t>
@@ -1534,7 +1534,7 @@
     <t>table__dbo.AWBuildVersion.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__dbo.AWBuildVersion.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__dbo.AWBuildVersion.sql</t>
   </si>
   <si>
     <t>Incorrect Analysis Warning: 1, Total Statement count: 1, Conventional Statement count: 1, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 0, High category breaks: 0</t>
@@ -1549,7 +1549,7 @@
     <t>table__dbo.DatabaseLog.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__dbo.DatabaseLog.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__dbo.DatabaseLog.sql</t>
   </si>
   <si>
     <t>F0343BA0E4E0A37B096257477CFF2588</t>
@@ -1561,7 +1561,7 @@
     <t>table__dbo.ErrorLog.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__dbo.ErrorLog.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/table__dbo.ErrorLog.sql</t>
   </si>
   <si>
     <t>4163DE2662EE1C6C040E46334FE032D2</t>
@@ -1573,7 +1573,7 @@
     <t>view__HumanResources.vEmployee.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vEmployee.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vEmployee.sql</t>
   </si>
   <si>
     <t>CREATE_VIEW</t>
@@ -1588,7 +1588,7 @@
     <t>view__HumanResources.vEmployeeDepartment.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartment.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartment.sql</t>
   </si>
   <si>
     <t>679B2E1E4FFFF228E3C17A5AF6EAB185</t>
@@ -1600,7 +1600,7 @@
     <t>view__HumanResources.vEmployeeDepartmentHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartmentHistory.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartmentHistory.sql</t>
   </si>
   <si>
     <t>50C7657DBE2E158414B1BEE40DE7858D</t>
@@ -1612,7 +1612,7 @@
     <t>view__HumanResources.vJobCandidate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidate.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidate.sql</t>
   </si>
   <si>
     <t>CREATE_VIEW,UNKNOWN,VAR_DECLARE</t>
@@ -1630,7 +1630,7 @@
     <t>view__HumanResources.vJobCandidateEducation.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEducation.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEducation.sql</t>
   </si>
   <si>
     <t>Incorrect Analysis Warning: 1, Total Statement count: 14, Conventional Statement count: 14, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1645,7 +1645,7 @@
     <t>view__HumanResources.vJobCandidateEmployment.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEmployment.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEmployment.sql</t>
   </si>
   <si>
     <t>Incorrect Analysis Warning: 1, Total Statement count: 12, Conventional Statement count: 12, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1660,7 +1660,7 @@
     <t>view__Person.vAdditionalContactInfo.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Person.vAdditionalContactInfo.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Person.vAdditionalContactInfo.sql</t>
   </si>
   <si>
     <t>Total Statement count: 24, Conventional Statement count: 13, Simple Statement count: 11, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1675,7 +1675,7 @@
     <t>view__Person.vStateProvinceCountryRegion.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Person.vStateProvinceCountryRegion.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Person.vStateProvinceCountryRegion.sql</t>
   </si>
   <si>
     <t>D1B666575C3150FA07161F6E1A8129F0</t>
@@ -1687,7 +1687,7 @@
     <t>view__Production.vProductAndDescription.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Production.vProductAndDescription.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Production.vProductAndDescription.sql</t>
   </si>
   <si>
     <t>AD0C95888E8820742BAA5DE17B3A96AA</t>
@@ -1699,7 +1699,7 @@
     <t>view__Production.vProductModelCatalogDescription.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Production.vProductModelCatalogDescription.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Production.vProductModelCatalogDescription.sql</t>
   </si>
   <si>
     <t>Total Statement count: 32, Conventional Statement count: 22, Simple Statement count: 10, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1714,7 +1714,7 @@
     <t>view__Production.vProductModelInstructions.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Production.vProductModelInstructions.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Production.vProductModelInstructions.sql</t>
   </si>
   <si>
     <t>1A47F8B4BC2B7ACEDB60EE1B1AAD4470</t>
@@ -1726,7 +1726,7 @@
     <t>view__Purchasing.vVendorWithAddresses.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithAddresses.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithAddresses.sql</t>
   </si>
   <si>
     <t>D7CD68F5F89F8956B1DBD51AB75496CB</t>
@@ -1738,7 +1738,7 @@
     <t>view__Purchasing.vVendorWithContacts.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithContacts.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithContacts.sql</t>
   </si>
   <si>
     <t>8FCD0C6976595D45BF4770D9FAA0EC11</t>
@@ -1750,7 +1750,7 @@
     <t>view__Sales.vIndividualCustomer.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vIndividualCustomer.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vIndividualCustomer.sql</t>
   </si>
   <si>
     <t>AA4431CE6421DCB43574B5BCCB8273B5</t>
@@ -1762,7 +1762,7 @@
     <t>view__Sales.vPersonDemographics.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vPersonDemographics.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vPersonDemographics.sql</t>
   </si>
   <si>
     <t>Total Statement count: 14, Conventional Statement count: 14, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1777,7 +1777,7 @@
     <t>view__Sales.vSalesPerson.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vSalesPerson.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vSalesPerson.sql</t>
   </si>
   <si>
     <t>090AE69AE0362DEA70853EFBAE038CE7</t>
@@ -1789,7 +1789,7 @@
     <t>view__Sales.vSalesPersonSalesByFiscalYears.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vSalesPersonSalesByFiscalYears.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vSalesPersonSalesByFiscalYears.sql</t>
   </si>
   <si>
     <t>Total Statement count: 1, Conventional Statement count: 1, Simple Statement count: 0, Pivot functions: 1, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1804,7 +1804,7 @@
     <t>view__Sales.vStoreWithAddresses.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vStoreWithAddresses.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vStoreWithAddresses.sql</t>
   </si>
   <si>
     <t>0AFF094C65B3C3F48B8130C48F8F6294</t>
@@ -1816,7 +1816,7 @@
     <t>view__Sales.vStoreWithContacts.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vStoreWithContacts.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vStoreWithContacts.sql</t>
   </si>
   <si>
     <t>C707BD34FAA1443727F92838D30983B9</t>
@@ -1828,7 +1828,7 @@
     <t>view__Sales.vStoreWithDemographics.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vStoreWithDemographics.sql</t>
+    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vStoreWithDemographics.sql</t>
   </si>
   <si>
     <t>06140F8E409F58532DAB1C311FA4E9B9</t>
@@ -2047,36 +2047,39 @@
     <t>ISNULL</t>
   </si>
   <si>
+    <t>TEXT</t>
+  </si>
+  <si>
     <t>COALESCE</t>
   </si>
   <si>
-    <t>TEXT</t>
-  </si>
-  <si>
     <t>OPTION</t>
   </si>
   <si>
+    <t>CONTAINSTABLE</t>
+  </si>
+  <si>
     <t>ERROR_NUMBER</t>
   </si>
   <si>
-    <t>CONTAINSTABLE</t>
-  </si>
-  <si>
     <t>ERROR_MESSAGE</t>
   </si>
   <si>
+    <t>ERROR_LINE</t>
+  </si>
+  <si>
+    <t>DATEADD</t>
+  </si>
+  <si>
     <t>SQL:COLUMN</t>
   </si>
   <si>
-    <t>DATEADD</t>
+    <t>OF</t>
   </si>
   <si>
     <t>ERROR_STATE</t>
   </si>
   <si>
-    <t>OF</t>
-  </si>
-  <si>
     <t>RAISERROR</t>
   </si>
   <si>
@@ -2086,43 +2089,40 @@
     <t>ERROR_SEVERITY</t>
   </si>
   <si>
-    <t>ERROR_LINE</t>
+    <t>REPLICATE</t>
+  </si>
+  <si>
+    <t>NUMERIC</t>
+  </si>
+  <si>
+    <t>REPLACE</t>
   </si>
   <si>
     <t>DATALENGTH</t>
   </si>
   <si>
+    <t>COUNT</t>
+  </si>
+  <si>
+    <t>SERVERPROPERTY</t>
+  </si>
+  <si>
+    <t>YEAR</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>INTO</t>
+  </si>
+  <si>
+    <t>PIVOT</t>
+  </si>
+  <si>
+    <t>XACT_STATE</t>
+  </si>
+  <si>
     <t>FREETEXTTABLE</t>
-  </si>
-  <si>
-    <t>REPLICATE</t>
-  </si>
-  <si>
-    <t>STRING</t>
-  </si>
-  <si>
-    <t>YEAR</t>
-  </si>
-  <si>
-    <t>XACT_STATE</t>
-  </si>
-  <si>
-    <t>SERVERPROPERTY</t>
-  </si>
-  <si>
-    <t>COUNT</t>
-  </si>
-  <si>
-    <t>REPLACE</t>
-  </si>
-  <si>
-    <t>INTO</t>
-  </si>
-  <si>
-    <t>NUMERIC</t>
-  </si>
-  <si>
-    <t>PIVOT</t>
   </si>
   <si>
     <t>Script</t>
@@ -3573,10 +3573,10 @@
         <v>703</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>704</v>
@@ -5339,7 +5339,7 @@
         <v>153</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>698</v>
@@ -5353,7 +5353,7 @@
         <v>153</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>698</v>
@@ -9154,7 +9154,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="6" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="B21" s="6">
         <v>1</v>
@@ -14864,18 +14864,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>206</v>
+        <v>574</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="C2" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>663</v>
@@ -14886,54 +14886,54 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>390</v>
+        <v>434</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>664</v>
       </c>
       <c r="C4" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>390</v>
+        <v>286</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C5" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>553</v>
+        <v>286</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C6" s="6">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>140</v>
+        <v>414</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="C7" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
@@ -14941,21 +14941,21 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>140</v>
+        <v>362</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
       <c r="C9" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
-        <v>140</v>
+        <v>358</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
@@ -14963,10 +14963,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -14985,10 +14985,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
-        <v>140</v>
+        <v>386</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -14996,21 +14996,21 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
-        <v>140</v>
+        <v>486</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C14" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
-        <v>535</v>
+        <v>402</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>691</v>
+        <v>664</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -15018,32 +15018,32 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>535</v>
+        <v>298</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C16" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
-        <v>535</v>
+        <v>298</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C17" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
-        <v>278</v>
+        <v>177</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
@@ -15051,21 +15051,21 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
-        <v>254</v>
+        <v>535</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C19" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>326</v>
+        <v>535</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
@@ -15073,21 +15073,21 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
-        <v>370</v>
+        <v>535</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>663</v>
+        <v>685</v>
       </c>
       <c r="C21" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="6" t="s">
-        <v>246</v>
+        <v>76</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
@@ -15095,10 +15095,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
@@ -15106,10 +15106,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>51</v>
+        <v>558</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="C24" s="6">
         <v>1</v>
@@ -15117,21 +15117,21 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>290</v>
+        <v>558</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C25" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>153</v>
+        <v>558</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C26" s="6">
         <v>1</v>
@@ -15139,29 +15139,29 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>153</v>
+        <v>334</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C27" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>153</v>
+        <v>507</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>684</v>
+        <v>663</v>
       </c>
       <c r="C28" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>153</v>
+        <v>270</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>663</v>
@@ -15172,10 +15172,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="C30" s="6">
         <v>1</v>
@@ -15183,54 +15183,54 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="6" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C31" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="6" t="s">
-        <v>486</v>
+        <v>218</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>663</v>
+        <v>615</v>
       </c>
       <c r="C32" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>470</v>
+        <v>218</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C33" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
-        <v>362</v>
+        <v>474</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C34" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>358</v>
+        <v>290</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C35" s="6">
         <v>1</v>
@@ -15238,21 +15238,21 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>422</v>
+        <v>503</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C36" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>422</v>
+        <v>100</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>663</v>
+        <v>686</v>
       </c>
       <c r="C37" s="6">
         <v>1</v>
@@ -15260,10 +15260,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="6" t="s">
-        <v>294</v>
+        <v>100</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C38" s="6">
         <v>1</v>
@@ -15271,10 +15271,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="C39" s="6">
         <v>1</v>
@@ -15282,21 +15282,21 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="C40" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>136</v>
+        <v>326</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C41" s="6">
         <v>1</v>
@@ -15304,29 +15304,29 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="6" t="s">
-        <v>524</v>
+        <v>426</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C42" s="6">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="6" t="s">
-        <v>596</v>
+        <v>206</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>663</v>
+        <v>615</v>
       </c>
       <c r="C43" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="6" t="s">
-        <v>414</v>
+        <v>294</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>663</v>
@@ -15337,10 +15337,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="6" t="s">
-        <v>189</v>
+        <v>382</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>690</v>
+        <v>664</v>
       </c>
       <c r="C45" s="6">
         <v>1</v>
@@ -15348,10 +15348,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="6" t="s">
-        <v>189</v>
+        <v>430</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="C46" s="6">
         <v>1</v>
@@ -15362,7 +15362,7 @@
         <v>430</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C47" s="6">
         <v>1</v>
@@ -15370,10 +15370,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="6" t="s">
-        <v>430</v>
+        <v>195</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C48" s="6">
         <v>1</v>
@@ -15381,21 +15381,21 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="6" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>615</v>
+        <v>666</v>
       </c>
       <c r="C49" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="6" t="s">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>692</v>
+        <v>665</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -15403,65 +15403,65 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="6" t="s">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="C51" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="6" t="s">
-        <v>201</v>
+        <v>370</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C52" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="6" t="s">
-        <v>201</v>
+        <v>470</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="C53" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="6" t="s">
-        <v>310</v>
+        <v>171</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>664</v>
+        <v>615</v>
       </c>
       <c r="C54" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="6" t="s">
-        <v>310</v>
+        <v>171</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>663</v>
+        <v>691</v>
       </c>
       <c r="C55" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="6" t="s">
-        <v>165</v>
+        <v>310</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="C56" s="6">
         <v>1</v>
@@ -15469,54 +15469,54 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="6" t="s">
-        <v>230</v>
+        <v>310</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C57" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="6" t="s">
-        <v>230</v>
+        <v>302</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>664</v>
       </c>
       <c r="C58" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="6" t="s">
-        <v>574</v>
+        <v>322</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C59" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="6" t="s">
-        <v>494</v>
+        <v>322</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C60" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="6" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C61" s="6">
         <v>1</v>
@@ -15524,10 +15524,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="6" t="s">
-        <v>378</v>
+        <v>70</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -15535,10 +15535,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="6" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>615</v>
+        <v>667</v>
       </c>
       <c r="C63" s="6">
         <v>2</v>
@@ -15546,32 +15546,32 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="6" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>667</v>
+        <v>615</v>
       </c>
       <c r="C64" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="6" t="s">
-        <v>298</v>
+        <v>201</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C65" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="6" t="s">
-        <v>298</v>
+        <v>136</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -15579,10 +15579,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="6" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C67" s="6">
         <v>1</v>
@@ -15590,32 +15590,32 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="6" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="C68" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="6" t="s">
-        <v>147</v>
+        <v>212</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C69" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="6" t="s">
-        <v>147</v>
+        <v>212</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>681</v>
+        <v>666</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -15623,32 +15623,32 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="6" t="s">
-        <v>147</v>
+        <v>212</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="C71" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="6" t="s">
-        <v>147</v>
+        <v>212</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>674</v>
+        <v>615</v>
       </c>
       <c r="C72" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="6" t="s">
-        <v>147</v>
+        <v>212</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="C73" s="6">
         <v>1</v>
@@ -15656,10 +15656,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="6" t="s">
-        <v>147</v>
+        <v>494</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -15667,43 +15667,43 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="6" t="s">
-        <v>322</v>
+        <v>446</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>663</v>
+        <v>684</v>
       </c>
       <c r="C75" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="6" t="s">
-        <v>322</v>
+        <v>446</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C76" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="6" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="C77" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="6" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>665</v>
+        <v>688</v>
       </c>
       <c r="C78" s="6">
         <v>1</v>
@@ -15711,10 +15711,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="6" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>683</v>
+        <v>665</v>
       </c>
       <c r="C79" s="6">
         <v>1</v>
@@ -15722,10 +15722,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="6" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C80" s="6">
         <v>1</v>
@@ -15733,43 +15733,43 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="6" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>668</v>
+        <v>694</v>
       </c>
       <c r="C81" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="6" t="s">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C82" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="6" t="s">
-        <v>218</v>
+        <v>524</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C83" s="6">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="6" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="C84" s="6">
         <v>2</v>
@@ -15777,10 +15777,10 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="6" t="s">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C85" s="6">
         <v>1</v>
@@ -15788,21 +15788,21 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="6" t="s">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C86" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="6" t="s">
-        <v>318</v>
+        <v>390</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C87" s="6">
         <v>1</v>
@@ -15810,10 +15810,10 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="6" t="s">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C88" s="6">
         <v>1</v>
@@ -15821,32 +15821,32 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="6" t="s">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C89" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="6" t="s">
-        <v>498</v>
+        <v>230</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C90" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="6" t="s">
-        <v>374</v>
+        <v>583</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>663</v>
+        <v>692</v>
       </c>
       <c r="C91" s="6">
         <v>1</v>
@@ -15854,10 +15854,10 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="6" t="s">
-        <v>94</v>
+        <v>583</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>666</v>
+        <v>689</v>
       </c>
       <c r="C92" s="6">
         <v>1</v>
@@ -15865,10 +15865,10 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="6" t="s">
-        <v>128</v>
+        <v>583</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C93" s="6">
         <v>1</v>
@@ -15876,10 +15876,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="6" t="s">
-        <v>212</v>
+        <v>583</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C94" s="6">
         <v>1</v>
@@ -15887,43 +15887,43 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="6" t="s">
-        <v>212</v>
+        <v>583</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="C95" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="6" t="s">
-        <v>212</v>
+        <v>482</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="C96" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="6" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>615</v>
+        <v>666</v>
       </c>
       <c r="C97" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="6" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C98" s="6">
         <v>1</v>
@@ -15931,7 +15931,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="6" t="s">
-        <v>482</v>
+        <v>374</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>663</v>
@@ -15942,40 +15942,40 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="6" t="s">
-        <v>306</v>
+        <v>530</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C100" s="6">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="6" t="s">
-        <v>306</v>
+        <v>450</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C101" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="6" t="s">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C102" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="6" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>665</v>
@@ -15986,51 +15986,51 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="6" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C104" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="6" t="s">
-        <v>530</v>
+        <v>422</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C105" s="6">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="6" t="s">
-        <v>540</v>
+        <v>422</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C106" s="6">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="6" t="s">
-        <v>540</v>
+        <v>498</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C107" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="6" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>663</v>
@@ -16041,10 +16041,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="6" t="s">
-        <v>334</v>
+        <v>122</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C109" s="6">
         <v>1</v>
@@ -16052,21 +16052,21 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="6" t="s">
-        <v>474</v>
+        <v>122</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="C110" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="6" t="s">
-        <v>446</v>
+        <v>122</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>693</v>
+        <v>666</v>
       </c>
       <c r="C111" s="6">
         <v>1</v>
@@ -16074,7 +16074,7 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="6" t="s">
-        <v>446</v>
+        <v>278</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>663</v>
@@ -16085,32 +16085,32 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="6" t="s">
-        <v>70</v>
+        <v>540</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>669</v>
       </c>
       <c r="C113" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="6" t="s">
-        <v>70</v>
+        <v>540</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="6" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C115" s="6">
         <v>1</v>
@@ -16118,21 +16118,21 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="6" t="s">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="C116" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="6" t="s">
-        <v>286</v>
+        <v>140</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>664</v>
+        <v>679</v>
       </c>
       <c r="C117" s="6">
         <v>1</v>
@@ -16140,21 +16140,21 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="6" t="s">
-        <v>286</v>
+        <v>140</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="C118" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="6" t="s">
-        <v>302</v>
+        <v>140</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="C119" s="6">
         <v>1</v>
@@ -16162,43 +16162,43 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="6" t="s">
-        <v>507</v>
+        <v>140</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C120" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="6" t="s">
-        <v>418</v>
+        <v>140</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="C121" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="6" t="s">
-        <v>450</v>
+        <v>140</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C122" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="6" t="s">
-        <v>583</v>
+        <v>140</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C123" s="6">
         <v>1</v>
@@ -16206,32 +16206,32 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="6" t="s">
-        <v>583</v>
+        <v>553</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>694</v>
+        <v>663</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="6" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C125" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="6" t="s">
-        <v>583</v>
+        <v>147</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -16239,10 +16239,10 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="6" t="s">
-        <v>583</v>
+        <v>147</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="C127" s="6">
         <v>1</v>
@@ -16250,43 +16250,43 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="6" t="s">
-        <v>426</v>
+        <v>147</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C128" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="6" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="C129" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="6" t="s">
-        <v>386</v>
+        <v>147</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C130" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="6" t="s">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="C131" s="6">
         <v>1</v>
@@ -16294,10 +16294,10 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="6" t="s">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -16305,10 +16305,10 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="6" t="s">
-        <v>350</v>
+        <v>147</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="C133" s="6">
         <v>1</v>
@@ -16316,43 +16316,43 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="6" t="s">
-        <v>382</v>
+        <v>183</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>664</v>
+        <v>615</v>
       </c>
       <c r="C134" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="6" t="s">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C135" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="6" t="s">
-        <v>466</v>
+        <v>350</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C136" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="6" t="s">
-        <v>558</v>
+        <v>306</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C137" s="6">
         <v>1</v>
@@ -16360,24 +16360,24 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="6" t="s">
-        <v>558</v>
+        <v>306</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C138" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="6" t="s">
-        <v>558</v>
+        <v>250</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>686</v>
+        <v>663</v>
       </c>
       <c r="C139" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16500,15 +16500,15 @@
     </row>
     <row r="2" spans="1:34">
       <c r="A2" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D2" s="6">
-        <v>1</v>
+        <v>574</v>
+      </c>
+      <c r="B2" s="6">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:34">
       <c r="A3" s="6" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B3" s="6">
         <v>1</v>
@@ -16516,800 +16516,800 @@
     </row>
     <row r="4" spans="1:34">
       <c r="A4" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
+        <v>434</v>
       </c>
       <c r="C4" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:34">
       <c r="A5" s="6" t="s">
-        <v>553</v>
+        <v>286</v>
       </c>
       <c r="B5" s="6">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:34">
       <c r="A6" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="L6" s="6">
-        <v>2</v>
-      </c>
-      <c r="N6" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>1</v>
-      </c>
-      <c r="T6" s="6">
-        <v>1</v>
-      </c>
-      <c r="U6" s="6">
-        <v>1</v>
-      </c>
-      <c r="V6" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="6">
+        <v>414</v>
+      </c>
+      <c r="B6" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:34">
       <c r="A7" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="B7" s="6">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:34">
       <c r="A8" s="6" t="s">
-        <v>278</v>
+        <v>362</v>
       </c>
       <c r="B8" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:34">
       <c r="A9" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B9" s="6">
+        <v>358</v>
+      </c>
+      <c r="C9" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:34">
       <c r="A10" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B10" s="6">
+        <v>189</v>
+      </c>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:34">
       <c r="A11" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="B11" s="6">
-        <v>3</v>
+        <v>386</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:34">
       <c r="A12" s="6" t="s">
-        <v>246</v>
+        <v>486</v>
       </c>
       <c r="B12" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:34">
       <c r="A13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1</v>
-      </c>
-      <c r="P13" s="6">
+        <v>402</v>
+      </c>
+      <c r="C13" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:34">
       <c r="A14" s="6" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B14" s="6">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:34">
       <c r="A15" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1</v>
-      </c>
-      <c r="M15" s="6">
-        <v>3</v>
-      </c>
-      <c r="X15" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="6">
+        <v>177</v>
+      </c>
+      <c r="G15" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:34">
       <c r="A16" s="6" t="s">
-        <v>224</v>
+        <v>535</v>
       </c>
       <c r="B16" s="6">
+        <v>10</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
+      <c r="A17" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1</v>
+      </c>
+      <c r="J17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
+      <c r="A18" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="B18" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:32">
-      <c r="A17" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="B17" s="6">
+      <c r="I18" s="6">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30">
+      <c r="A19" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
+      <c r="A20" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B20" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:32">
-      <c r="A18" s="6" t="s">
+    <row r="21" spans="1:30">
+      <c r="A21" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
+      <c r="A22" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K22" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30">
+      <c r="A23" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
+      <c r="A24" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D24" s="6">
+        <v>2</v>
+      </c>
+      <c r="F24" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
+      <c r="A25" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B25" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
+      <c r="A26" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B26" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30">
+      <c r="A27" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="B27" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30">
+      <c r="A28" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
+      <c r="W28" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30">
+      <c r="A29" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="T29" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30">
+      <c r="A30" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B30" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30">
+      <c r="A31" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B31" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30">
+      <c r="A32" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31">
+      <c r="A33" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B33" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31">
+      <c r="A34" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31">
+      <c r="A35" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B35" s="6">
+        <v>1</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31">
+      <c r="A36" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F36" s="6">
+        <v>1</v>
+      </c>
+      <c r="G36" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31">
+      <c r="A37" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="6">
+        <v>1</v>
+      </c>
+      <c r="P37" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31">
+      <c r="A38" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B38" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31">
+      <c r="A39" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="B18" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:32">
-      <c r="A19" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="B19" s="6">
+      <c r="B39" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31">
+      <c r="A40" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D40" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:32">
-      <c r="A20" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32">
-      <c r="A21" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B21" s="6">
-        <v>1</v>
-      </c>
-      <c r="C21" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:32">
-      <c r="A22" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="B22" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32">
-      <c r="A23" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F23" s="6">
-        <v>1</v>
-      </c>
-      <c r="H23" s="6">
-        <v>2</v>
-      </c>
-      <c r="K23" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:32">
-      <c r="A24" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="B24" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:32">
-      <c r="A25" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="B25" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:32">
-      <c r="A26" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="B26" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:32">
-      <c r="A27" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="S27" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD27" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:32">
-      <c r="A28" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="B28" s="6">
-        <v>1</v>
-      </c>
-      <c r="C28" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:32">
-      <c r="A29" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D29" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF29" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:32">
-      <c r="A30" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D30" s="6">
-        <v>3</v>
-      </c>
-      <c r="F30" s="6">
-        <v>1</v>
-      </c>
-      <c r="G30" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:32">
-      <c r="A31" s="6" t="s">
+      <c r="AE40" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31">
+      <c r="A41" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="B31" s="6">
-        <v>4</v>
-      </c>
-      <c r="C31" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:32">
-      <c r="A32" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="S32" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25">
-      <c r="A33" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B33" s="6">
-        <v>3</v>
-      </c>
-      <c r="C33" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25">
-      <c r="A34" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="B34" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25">
-      <c r="A35" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="B35" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25">
-      <c r="A36" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="G36" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25">
-      <c r="A37" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="B37" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25">
-      <c r="A38" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D38" s="6">
-        <v>2</v>
-      </c>
-      <c r="G38" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25">
-      <c r="A39" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="B39" s="6">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25">
-      <c r="A40" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" s="6">
-        <v>4</v>
-      </c>
-      <c r="H40" s="6">
-        <v>1</v>
-      </c>
-      <c r="L40" s="6">
-        <v>1</v>
-      </c>
-      <c r="N40" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="6">
-        <v>1</v>
-      </c>
-      <c r="T40" s="6">
-        <v>1</v>
-      </c>
-      <c r="U40" s="6">
-        <v>1</v>
-      </c>
-      <c r="V40" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25">
-      <c r="A41" s="6" t="s">
-        <v>322</v>
       </c>
       <c r="B41" s="6">
         <v>4</v>
       </c>
       <c r="C41" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31">
+      <c r="A42" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31">
+      <c r="A43" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B43" s="6">
+        <v>4</v>
+      </c>
+      <c r="C43" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
-      <c r="A42" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E42" s="6">
-        <v>1</v>
-      </c>
-      <c r="W42" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y42" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25">
-      <c r="A43" s="6" t="s">
+    <row r="44" spans="1:31">
+      <c r="A44" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E44" s="6">
+        <v>1</v>
+      </c>
+      <c r="J44" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31">
+      <c r="A45" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D45" s="6">
+        <v>3</v>
+      </c>
+      <c r="F45" s="6">
+        <v>1</v>
+      </c>
+      <c r="G45" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31">
+      <c r="A46" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F46" s="6">
+        <v>1</v>
+      </c>
+      <c r="H46" s="6">
+        <v>2</v>
+      </c>
+      <c r="K46" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31">
+      <c r="A47" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D47" s="6">
+        <v>4</v>
+      </c>
+      <c r="F47" s="6">
+        <v>1</v>
+      </c>
+      <c r="G47" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>2</v>
+      </c>
+      <c r="R47" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31">
+      <c r="A48" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="B48" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:34">
+      <c r="A49" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B49" s="6">
+        <v>1</v>
+      </c>
+      <c r="X49" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:34">
+      <c r="A50" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="6">
+        <v>1</v>
+      </c>
+      <c r="E50" s="6">
+        <v>1</v>
+      </c>
+      <c r="L50" s="6">
+        <v>3</v>
+      </c>
+      <c r="AB50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:34">
+      <c r="A51" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B51" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:34">
+      <c r="A52" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B52" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:34">
+      <c r="A53" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B53" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:34">
+      <c r="A54" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K54" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:34">
+      <c r="A55" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B55" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:34">
+      <c r="A56" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B56" s="6">
+        <v>1</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:34">
+      <c r="A57" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B57" s="6">
+        <v>3</v>
+      </c>
+      <c r="C57" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:34">
+      <c r="A58" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="F58" s="6">
+        <v>1</v>
+      </c>
+      <c r="J58" s="6">
+        <v>1</v>
+      </c>
+      <c r="P58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:34">
+      <c r="A59" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B59" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:34">
+      <c r="A60" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:34">
+      <c r="A61" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B61" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:34">
+      <c r="A62" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B62" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:34">
+      <c r="A63" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="B63" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:34">
+      <c r="A64" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="B64" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33">
+      <c r="A65" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" s="6">
+        <v>1</v>
+      </c>
+      <c r="J65" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33">
+      <c r="A66" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B66" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33">
+      <c r="A67" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B67" s="6">
+        <v>1</v>
+      </c>
+      <c r="C67" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:33">
+      <c r="A68" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="B68" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:33">
+      <c r="A69" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B69" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33">
+      <c r="A70" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F43" s="6">
-        <v>1</v>
-      </c>
-      <c r="H43" s="6">
+      <c r="F70" s="6">
+        <v>1</v>
+      </c>
+      <c r="H70" s="6">
         <v>2</v>
       </c>
-      <c r="K43" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25">
-      <c r="A44" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D44" s="6">
+      <c r="K70" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33">
+      <c r="A71" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B71" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:33">
+      <c r="A72" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="B72" s="6">
+        <v>11</v>
+      </c>
+      <c r="I72" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:33">
+      <c r="A73" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="B73" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:33">
+      <c r="A74" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E74" s="6">
+        <v>1</v>
+      </c>
+      <c r="M74" s="6">
         <v>2</v>
       </c>
-      <c r="F44" s="6">
+      <c r="N74" s="6">
+        <v>1</v>
+      </c>
+      <c r="O74" s="6">
+        <v>1</v>
+      </c>
+      <c r="S74" s="6">
+        <v>1</v>
+      </c>
+      <c r="U74" s="6">
+        <v>1</v>
+      </c>
+      <c r="V74" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG74" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:33">
+      <c r="A75" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="B75" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:33">
+      <c r="A76" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="B76" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:33">
+      <c r="A77" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E77" s="6">
+        <v>4</v>
+      </c>
+      <c r="H77" s="6">
+        <v>1</v>
+      </c>
+      <c r="M77" s="6">
+        <v>1</v>
+      </c>
+      <c r="N77" s="6">
+        <v>1</v>
+      </c>
+      <c r="O77" s="6">
+        <v>1</v>
+      </c>
+      <c r="S77" s="6">
+        <v>1</v>
+      </c>
+      <c r="U77" s="6">
+        <v>1</v>
+      </c>
+      <c r="V77" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:33">
+      <c r="A78" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D78" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:25">
-      <c r="A45" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F45" s="6">
-        <v>1</v>
-      </c>
-      <c r="G45" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25">
-      <c r="A46" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B46" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25">
-      <c r="A47" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E47" s="6">
-        <v>1</v>
-      </c>
-      <c r="I47" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25">
-      <c r="A48" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="B48" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:33">
-      <c r="A49" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="B49" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:33">
-      <c r="A50" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F50" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:33">
-      <c r="A51" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="K51" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:33">
-      <c r="A52" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D52" s="6">
+      <c r="G78" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:33">
+      <c r="A79" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B79" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:33">
+      <c r="A80" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B80" s="6">
+        <v>1</v>
+      </c>
+      <c r="C80" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" s="6">
         <v>4</v>
-      </c>
-      <c r="F52" s="6">
-        <v>1</v>
-      </c>
-      <c r="G52" s="6">
-        <v>1</v>
-      </c>
-      <c r="O52" s="6">
-        <v>2</v>
-      </c>
-      <c r="R52" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:33">
-      <c r="A53" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="B53" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:33">
-      <c r="A54" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="B54" s="6">
-        <v>1</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:33">
-      <c r="A55" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="C55" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:33">
-      <c r="A56" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E56" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:33">
-      <c r="A57" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="C57" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:33">
-      <c r="A58" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="B58" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:33">
-      <c r="A59" s="6" t="s">
-        <v>540</v>
-      </c>
-      <c r="B59" s="6">
-        <v>11</v>
-      </c>
-      <c r="J59" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:33">
-      <c r="A60" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="B60" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:33">
-      <c r="A61" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="B61" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:33">
-      <c r="A62" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="B62" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:33">
-      <c r="A63" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="B63" s="6">
-        <v>1</v>
-      </c>
-      <c r="AG63" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:33">
-      <c r="A64" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E64" s="6">
-        <v>1</v>
-      </c>
-      <c r="I64" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:34">
-      <c r="A65" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K65" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:34">
-      <c r="A66" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B66" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:34">
-      <c r="A67" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="B67" s="6">
-        <v>5</v>
-      </c>
-      <c r="C67" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:34">
-      <c r="A68" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="C68" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:34">
-      <c r="A69" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="B69" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:34">
-      <c r="A70" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="B70" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:34">
-      <c r="A71" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="B71" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:34">
-      <c r="A72" s="6" t="s">
-        <v>583</v>
-      </c>
-      <c r="F72" s="6">
-        <v>1</v>
-      </c>
-      <c r="I72" s="6">
-        <v>1</v>
-      </c>
-      <c r="P72" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA72" s="6">
-        <v>1</v>
-      </c>
-      <c r="AH72" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:34">
-      <c r="A73" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="B73" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:34">
-      <c r="A74" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="B74" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:34">
-      <c r="A75" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="C75" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:34">
-      <c r="A76" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E76" s="6">
-        <v>1</v>
-      </c>
-      <c r="I76" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:34">
-      <c r="A77" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="B77" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:34">
-      <c r="A78" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="C78" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:34">
-      <c r="A79" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B79" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:34">
-      <c r="A80" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="B80" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:26">
-      <c r="A81" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="B81" s="6">
-        <v>2</v>
-      </c>
-      <c r="J81" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z81" s="6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -17359,7 +17359,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C3" s="8">
         <v>3</v>
@@ -17367,7 +17367,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="C4" s="8">
         <v>1</v>

--- a/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.xlsx
+++ b/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="897">
   <si>
-    <t>Run date/time: 2026-07-06 20:48:37</t>
+    <t>Run date/time: 2026-07-07 11:16:22</t>
   </si>
   <si>
     <t>Code Base Details</t>
@@ -124,7 +124,7 @@
     <t>-d</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql</t>
   </si>
   <si>
     <t>-e</t>
@@ -133,13 +133,13 @@
     <t>-j</t>
   </si>
   <si>
-    <t>D:\autovista\output_lakebridge\reports\lakebridge_report_MS_SQL_Server.json</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.json</t>
   </si>
   <si>
     <t>-r</t>
   </si>
   <si>
-    <t>D:\autovista\output_lakebridge\reports\lakebridge_report_MS_SQL_Server.xlsx</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.xlsx</t>
   </si>
   <si>
     <t>-t</t>
@@ -151,7 +151,7 @@
     <t>Analyzer run duration:</t>
   </si>
   <si>
-    <t>0h, 0m, 4s</t>
+    <t>0h, 0m, 1s</t>
   </si>
   <si>
     <t>Program Name</t>
@@ -193,7 +193,7 @@
     <t>sql_scalar_function__dbo.ufnGetAccountingEndDate.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingEndDate.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingEndDate.sql</t>
   </si>
   <si>
     <t>YES</t>
@@ -220,7 +220,7 @@
     <t>sql_scalar_function__dbo.ufnGetAccountingStartDate.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingStartDate.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingStartDate.sql</t>
   </si>
   <si>
     <t>BAF6458A7E562903BA94D801522005A0</t>
@@ -232,7 +232,7 @@
     <t>sql_scalar_function__dbo.ufnGetDocumentStatusText.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetDocumentStatusText.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetDocumentStatusText.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -250,7 +250,7 @@
     <t>sql_scalar_function__dbo.ufnGetProductDealerPrice.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductDealerPrice.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductDealerPrice.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,SELECT_VAR_ASSIGNMENT,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -268,7 +268,7 @@
     <t>sql_scalar_function__dbo.ufnGetProductListPrice.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductListPrice.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductListPrice.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,SELECT_VAR_ASSIGNMENT,UNKNOWN,VAR_DECLARE</t>
@@ -286,7 +286,7 @@
     <t>sql_scalar_function__dbo.ufnGetProductStandardCost.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductStandardCost.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductStandardCost.sql</t>
   </si>
   <si>
     <t>8F43C9F49781DB147EE70E52AF3E8C18</t>
@@ -298,7 +298,7 @@
     <t>sql_scalar_function__dbo.ufnGetPurchaseOrderStatusText.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetPurchaseOrderStatusText.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetPurchaseOrderStatusText.sql</t>
   </si>
   <si>
     <t>65A240477CA9503CB1F2D199C2B26A96</t>
@@ -310,7 +310,7 @@
     <t>sql_scalar_function__dbo.ufnGetSalesOrderStatusText.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetSalesOrderStatusText.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetSalesOrderStatusText.sql</t>
   </si>
   <si>
     <t>0B4FB00504955E9B32739F20AE320DF0</t>
@@ -322,7 +322,7 @@
     <t>sql_scalar_function__dbo.ufnGetStock.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetStock.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetStock.sql</t>
   </si>
   <si>
     <t>IF_START,PROGRAM_DECLARATION,SELECT_VAR_ASSIGNMENT,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -340,7 +340,7 @@
     <t>sql_scalar_function__dbo.ufnLeadingZeros.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnLeadingZeros.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnLeadingZeros.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -358,7 +358,7 @@
     <t>sql_stored_procedure__HumanResources.uspUpdateEmployeeHireInfo.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeHireInfo.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeHireInfo.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,DYNAMIC_SQL,IF_START,INSERT_INTO,UNKNOWN,UPDATE</t>
@@ -376,7 +376,7 @@
     <t>sql_stored_procedure__HumanResources.uspUpdateEmployeeLogin.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeLogin.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeLogin.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,DYNAMIC_SQL,UNKNOWN,UPDATE</t>
@@ -394,7 +394,7 @@
     <t>sql_stored_procedure__HumanResources.uspUpdateEmployeePersonalInfo.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeePersonalInfo.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeePersonalInfo.sql</t>
   </si>
   <si>
     <t>1150510C0F295A53ABB21132050E1842</t>
@@ -406,7 +406,7 @@
     <t>sql_stored_procedure__dbo.uspGetBillOfMaterials.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetBillOfMaterials.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetBillOfMaterials.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,WITH</t>
@@ -424,7 +424,7 @@
     <t>sql_stored_procedure__dbo.uspGetEmployeeManagers.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetEmployeeManagers.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetEmployeeManagers.sql</t>
   </si>
   <si>
     <t>2D5E9F29ED5FDBF0970D8E1DEB7EF7EF</t>
@@ -436,7 +436,7 @@
     <t>sql_stored_procedure__dbo.uspGetManagerEmployees.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetManagerEmployees.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetManagerEmployees.sql</t>
   </si>
   <si>
     <t>8B11ABC3F784D412FED8C567819B2188</t>
@@ -448,7 +448,7 @@
     <t>sql_stored_procedure__dbo.uspGetWhereUsedProductID.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetWhereUsedProductID.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetWhereUsedProductID.sql</t>
   </si>
   <si>
     <t>8FFD5EAF979D3F33C7B8447189E5CC10</t>
@@ -460,7 +460,7 @@
     <t>sql_stored_procedure__dbo.uspLogError.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspLogError.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspLogError.sql</t>
   </si>
   <si>
     <t>MEDIUM</t>
@@ -481,7 +481,7 @@
     <t>sql_stored_procedure__dbo.uspPrintError.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspPrintError.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspPrintError.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,UNKNOWN</t>
@@ -499,7 +499,7 @@
     <t>sql_stored_procedure__dbo.uspSearchCandidateResumes.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspSearchCandidateResumes.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspSearchCandidateResumes.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,DYNAMIC_SQL,ELSE_IF,IF_START,SELECT_VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -517,7 +517,7 @@
     <t>sql_table_valued_function__dbo.ufnGetContactInformation.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_table_valued_function__dbo.ufnGetContactInformation.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_table_valued_function__dbo.ufnGetContactInformation.sql</t>
   </si>
   <si>
     <t>IF_START,INSERT_INTO,PROGRAM_DECLARATION,UNKNOWN</t>
@@ -535,7 +535,7 @@
     <t>sql_trigger__HumanResources.dEmployee.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__HumanResources.dEmployee.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__HumanResources.dEmployee.sql</t>
   </si>
   <si>
     <t>DELETE,FOR,IF_START,SET,TRIGGER,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -553,7 +553,7 @@
     <t>sql_trigger__Person.iuPerson.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Person.iuPerson.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Person.iuPerson.sql</t>
   </si>
   <si>
     <t>FOR,IF_START,INSERT,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -571,7 +571,7 @@
     <t>sql_trigger__Production.iWorkOrder.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Production.iWorkOrder.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Production.iWorkOrder.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,INSERT,INSERT_INTO,SET,TRIGGER,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -589,7 +589,7 @@
     <t>sql_trigger__Production.uWorkOrder.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Production.uWorkOrder.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Production.uWorkOrder.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,INSERT_INTO,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -607,7 +607,7 @@
     <t>sql_trigger__Purchasing.dVendor.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.dVendor.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.dVendor.sql</t>
   </si>
   <si>
     <t>DELETE,DYNAMIC_SQL,FOR,IF_START,SELECT_VAR_ASSIGNMENT,SET,TRIGGER,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -625,7 +625,7 @@
     <t>sql_trigger__Purchasing.iPurchaseOrderDetail.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.iPurchaseOrderDetail.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.iPurchaseOrderDetail.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,INSERT,INSERT_INTO,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -643,7 +643,7 @@
     <t>sql_trigger__Purchasing.uPurchaseOrderDetail.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderDetail.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderDetail.sql</t>
   </si>
   <si>
     <t>Total Statement count: 22, Conventional Statement count: 14, Simple Statement count: 8, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -658,7 +658,7 @@
     <t>sql_trigger__Purchasing.uPurchaseOrderHeader.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderHeader.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderHeader.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -676,7 +676,7 @@
     <t>sql_trigger__Sales.iduSalesOrderDetail.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Sales.iduSalesOrderDetail.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Sales.iduSalesOrderDetail.sql</t>
   </si>
   <si>
     <t>DELETE,DYNAMIC_SQL,IF_START,INSERT_INTO,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -694,7 +694,7 @@
     <t>sql_trigger__Sales.uSalesOrderHeader.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/sql_trigger__Sales.uSalesOrderHeader.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Sales.uSalesOrderHeader.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,FOR,IF_START,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -712,7 +712,7 @@
     <t>table__HumanResources.Department.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.Department.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.Department.sql</t>
   </si>
   <si>
     <t>TABLE_DDL</t>
@@ -730,7 +730,7 @@
     <t>table__HumanResources.Employee.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.Employee.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.Employee.sql</t>
   </si>
   <si>
     <t>A09D1501EFF964FC7F93C28EF51C360A</t>
@@ -742,7 +742,7 @@
     <t>table__HumanResources.EmployeeDepartmentHistory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.EmployeeDepartmentHistory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.EmployeeDepartmentHistory.sql</t>
   </si>
   <si>
     <t>9228830EC44A62F7A7D2C8F41850032F</t>
@@ -754,7 +754,7 @@
     <t>table__HumanResources.EmployeePayHistory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.EmployeePayHistory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.EmployeePayHistory.sql</t>
   </si>
   <si>
     <t>42D4CA98D5026067D7084C89A9AF12B6</t>
@@ -766,7 +766,7 @@
     <t>table__HumanResources.JobCandidate.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.JobCandidate.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.JobCandidate.sql</t>
   </si>
   <si>
     <t>D678671C1A1D596D2DFB28AF39E3DBBC</t>
@@ -778,7 +778,7 @@
     <t>table__HumanResources.Shift.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__HumanResources.Shift.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.Shift.sql</t>
   </si>
   <si>
     <t>0839B989DA5FCAF2B2737EBC540D47FA</t>
@@ -790,7 +790,7 @@
     <t>table__Person.Address.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.Address.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.Address.sql</t>
   </si>
   <si>
     <t>485B09A2BAF22C3CD474D91BB496DDA3</t>
@@ -802,7 +802,7 @@
     <t>table__Person.AddressType.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.AddressType.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.AddressType.sql</t>
   </si>
   <si>
     <t>08B4363009B611557F05C437003C683F</t>
@@ -814,7 +814,7 @@
     <t>table__Person.BusinessEntity.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.BusinessEntity.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.BusinessEntity.sql</t>
   </si>
   <si>
     <t>9A22940EBB8A151E20E568F9C55DF1AE</t>
@@ -826,7 +826,7 @@
     <t>table__Person.BusinessEntityAddress.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.BusinessEntityAddress.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.BusinessEntityAddress.sql</t>
   </si>
   <si>
     <t>526B5BBA957622BBC2F5259A809EACD6</t>
@@ -838,7 +838,7 @@
     <t>table__Person.BusinessEntityContact.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.BusinessEntityContact.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.BusinessEntityContact.sql</t>
   </si>
   <si>
     <t>5B8957D0AC73C90AB40E85FBA5364190</t>
@@ -850,7 +850,7 @@
     <t>table__Person.ContactType.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.ContactType.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.ContactType.sql</t>
   </si>
   <si>
     <t>5E5B91699E103EB7CFF0FCB8160603BA</t>
@@ -862,7 +862,7 @@
     <t>table__Person.CountryRegion.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.CountryRegion.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.CountryRegion.sql</t>
   </si>
   <si>
     <t>5BB96BCDDBBDEBADF135B661C19B350B</t>
@@ -874,7 +874,7 @@
     <t>table__Person.EmailAddress.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.EmailAddress.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.EmailAddress.sql</t>
   </si>
   <si>
     <t>4B896C74F29899543C11EC768F32409B</t>
@@ -886,7 +886,7 @@
     <t>table__Person.Password.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.Password.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.Password.sql</t>
   </si>
   <si>
     <t>2E2A0FE95B210391BE42F9071EDE48BE</t>
@@ -898,7 +898,7 @@
     <t>table__Person.Person.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.Person.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.Person.sql</t>
   </si>
   <si>
     <t>CEA71116F62DA77C29D73CA35A022768</t>
@@ -910,7 +910,7 @@
     <t>table__Person.PersonPhone.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.PersonPhone.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.PersonPhone.sql</t>
   </si>
   <si>
     <t>60F9C8F4F9550E33504D90B5A74C70CC</t>
@@ -922,7 +922,7 @@
     <t>table__Person.PhoneNumberType.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.PhoneNumberType.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.PhoneNumberType.sql</t>
   </si>
   <si>
     <t>DBA25BAC265188C8967469364B9CE7FA</t>
@@ -934,7 +934,7 @@
     <t>table__Person.StateProvince.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Person.StateProvince.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.StateProvince.sql</t>
   </si>
   <si>
     <t>57D5CF4EEBA86A111B55FEEB79FFEDEC</t>
@@ -946,7 +946,7 @@
     <t>table__Production.BillOfMaterials.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.BillOfMaterials.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.BillOfMaterials.sql</t>
   </si>
   <si>
     <t>B41188C3DFF17B6A689AC8102D2BC1A6</t>
@@ -958,7 +958,7 @@
     <t>table__Production.Culture.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.Culture.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Culture.sql</t>
   </si>
   <si>
     <t>1C130C6BDF76C57176E59BF82D6F45E3</t>
@@ -970,7 +970,7 @@
     <t>table__Production.Document.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.Document.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Document.sql</t>
   </si>
   <si>
     <t>87223ADE7453748D59A4D77AB9161990</t>
@@ -982,7 +982,7 @@
     <t>table__Production.Illustration.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.Illustration.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Illustration.sql</t>
   </si>
   <si>
     <t>CDF25A85A06B21D4F894436430687C5F</t>
@@ -994,7 +994,7 @@
     <t>table__Production.Location.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.Location.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Location.sql</t>
   </si>
   <si>
     <t>0545BD908EB198803B1693015A3CE02B</t>
@@ -1006,7 +1006,7 @@
     <t>table__Production.Product.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.Product.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Product.sql</t>
   </si>
   <si>
     <t>E1A2837A7C58D9A163BF2F99F4BA918D</t>
@@ -1018,7 +1018,7 @@
     <t>table__Production.ProductCategory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductCategory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductCategory.sql</t>
   </si>
   <si>
     <t>3E35F2E89EEF417646F4CB4FBC17592A</t>
@@ -1030,7 +1030,7 @@
     <t>table__Production.ProductCostHistory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductCostHistory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductCostHistory.sql</t>
   </si>
   <si>
     <t>4261C77ACD861463971A72947ADEF0EB</t>
@@ -1042,7 +1042,7 @@
     <t>table__Production.ProductDescription.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductDescription.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductDescription.sql</t>
   </si>
   <si>
     <t>0A97183ACE800325530795C427B00F6A</t>
@@ -1054,7 +1054,7 @@
     <t>table__Production.ProductDocument.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductDocument.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductDocument.sql</t>
   </si>
   <si>
     <t>0398181199286BC96BFF033204F24025</t>
@@ -1066,7 +1066,7 @@
     <t>table__Production.ProductInventory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductInventory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductInventory.sql</t>
   </si>
   <si>
     <t>46D249B5A8EFF075AB470002B5C668B6</t>
@@ -1078,7 +1078,7 @@
     <t>table__Production.ProductListPriceHistory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductListPriceHistory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductListPriceHistory.sql</t>
   </si>
   <si>
     <t>23E2E2CA129E8DD01419C2370395097F</t>
@@ -1090,7 +1090,7 @@
     <t>table__Production.ProductModel.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductModel.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductModel.sql</t>
   </si>
   <si>
     <t>D05E0BF2770E989EF1DE2CA52468EDF5</t>
@@ -1102,7 +1102,7 @@
     <t>table__Production.ProductModelIllustration.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductModelIllustration.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductModelIllustration.sql</t>
   </si>
   <si>
     <t>BD221B96177793334973969A64B4BEBC</t>
@@ -1114,7 +1114,7 @@
     <t>table__Production.ProductModelProductDescriptionCulture.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductModelProductDescriptionCulture.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductModelProductDescriptionCulture.sql</t>
   </si>
   <si>
     <t>F35D2447ADCD0DA859EAF287626D974A</t>
@@ -1126,7 +1126,7 @@
     <t>table__Production.ProductPhoto.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductPhoto.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductPhoto.sql</t>
   </si>
   <si>
     <t>03C219754DA19CB82B6FD396EB6F28C5</t>
@@ -1138,7 +1138,7 @@
     <t>table__Production.ProductProductPhoto.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductProductPhoto.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductProductPhoto.sql</t>
   </si>
   <si>
     <t>876476D3B77644342259555E0A10E5F1</t>
@@ -1150,7 +1150,7 @@
     <t>table__Production.ProductReview.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductReview.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductReview.sql</t>
   </si>
   <si>
     <t>7C377BBF6513688CA880F9F9D0F1D76E</t>
@@ -1162,7 +1162,7 @@
     <t>table__Production.ProductSubcategory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ProductSubcategory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductSubcategory.sql</t>
   </si>
   <si>
     <t>EA8F0B633FC9352809AB4AB26BDA306C</t>
@@ -1174,7 +1174,7 @@
     <t>table__Production.ScrapReason.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.ScrapReason.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ScrapReason.sql</t>
   </si>
   <si>
     <t>C2AD160F44D5EDD63F11596C05CCBA51</t>
@@ -1186,7 +1186,7 @@
     <t>table__Production.TransactionHistory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.TransactionHistory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.TransactionHistory.sql</t>
   </si>
   <si>
     <t>13719707E5535F85CF798C7F5DAF155B</t>
@@ -1198,7 +1198,7 @@
     <t>table__Production.TransactionHistoryArchive.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.TransactionHistoryArchive.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.TransactionHistoryArchive.sql</t>
   </si>
   <si>
     <t>544F70FCAE619680F6C9951951608CDD</t>
@@ -1210,7 +1210,7 @@
     <t>table__Production.UnitMeasure.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.UnitMeasure.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.UnitMeasure.sql</t>
   </si>
   <si>
     <t>E24E10E408A06B9F5C59D83FF0CA225D</t>
@@ -1222,7 +1222,7 @@
     <t>table__Production.WorkOrder.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.WorkOrder.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.WorkOrder.sql</t>
   </si>
   <si>
     <t>41344D16748C45BF0868FF364D49878E</t>
@@ -1234,7 +1234,7 @@
     <t>table__Production.WorkOrderRouting.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Production.WorkOrderRouting.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.WorkOrderRouting.sql</t>
   </si>
   <si>
     <t>B08836F89C3812FCAD7848493AC6C222</t>
@@ -1246,7 +1246,7 @@
     <t>table__Purchasing.ProductVendor.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Purchasing.ProductVendor.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.ProductVendor.sql</t>
   </si>
   <si>
     <t>9E2E628A6B381784205541577DB178F3</t>
@@ -1258,7 +1258,7 @@
     <t>table__Purchasing.PurchaseOrderDetail.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderDetail.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderDetail.sql</t>
   </si>
   <si>
     <t>36588C425A912EBB636171FA624E54CA</t>
@@ -1270,7 +1270,7 @@
     <t>table__Purchasing.PurchaseOrderHeader.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderHeader.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderHeader.sql</t>
   </si>
   <si>
     <t>B5FF0036905B4D6641D97D3DD82A9125</t>
@@ -1282,7 +1282,7 @@
     <t>table__Purchasing.ShipMethod.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Purchasing.ShipMethod.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.ShipMethod.sql</t>
   </si>
   <si>
     <t>53C0287AFAFB7FACD5130ABA4F5A63DC</t>
@@ -1294,7 +1294,7 @@
     <t>table__Purchasing.Vendor.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Purchasing.Vendor.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.Vendor.sql</t>
   </si>
   <si>
     <t>0C3481C46FCF8839B53FA1C7AF77D661</t>
@@ -1306,7 +1306,7 @@
     <t>table__Sales.CountryRegionCurrency.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.CountryRegionCurrency.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.CountryRegionCurrency.sql</t>
   </si>
   <si>
     <t>CB23C961AD6C0967CBCE83F7B7D4252F</t>
@@ -1318,7 +1318,7 @@
     <t>table__Sales.CreditCard.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.CreditCard.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.CreditCard.sql</t>
   </si>
   <si>
     <t>86C19DBC9CB4B9BE848969BB70852DB6</t>
@@ -1330,7 +1330,7 @@
     <t>table__Sales.Currency.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.Currency.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.Currency.sql</t>
   </si>
   <si>
     <t>49DA4C335C4301DABE0D4AC5791CA07F</t>
@@ -1342,7 +1342,7 @@
     <t>table__Sales.CurrencyRate.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.CurrencyRate.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.CurrencyRate.sql</t>
   </si>
   <si>
     <t>A58B28FFBB12FBB0CA0E3766DF35B07E</t>
@@ -1354,7 +1354,7 @@
     <t>table__Sales.Customer.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.Customer.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.Customer.sql</t>
   </si>
   <si>
     <t>E6FC49B6E1B25B07E04DF33CE45F4399</t>
@@ -1366,7 +1366,7 @@
     <t>table__Sales.PersonCreditCard.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.PersonCreditCard.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.PersonCreditCard.sql</t>
   </si>
   <si>
     <t>A241FDEF93235427CF91A5507973980F</t>
@@ -1378,7 +1378,7 @@
     <t>table__Sales.SalesOrderDetail.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesOrderDetail.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesOrderDetail.sql</t>
   </si>
   <si>
     <t>E1099694C073E244D0B1732BFE40C2AB</t>
@@ -1390,7 +1390,7 @@
     <t>table__Sales.SalesOrderHeader.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeader.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeader.sql</t>
   </si>
   <si>
     <t>7354A80681291374434F107181B3B86A</t>
@@ -1402,7 +1402,7 @@
     <t>table__Sales.SalesOrderHeaderSalesReason.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeaderSalesReason.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeaderSalesReason.sql</t>
   </si>
   <si>
     <t>7A24418F81E279698B5FF138D4BFB170</t>
@@ -1414,7 +1414,7 @@
     <t>table__Sales.SalesPerson.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesPerson.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesPerson.sql</t>
   </si>
   <si>
     <t>49179896BB64CA95587BABDD2A7E43D4</t>
@@ -1426,7 +1426,7 @@
     <t>table__Sales.SalesPersonQuotaHistory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesPersonQuotaHistory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesPersonQuotaHistory.sql</t>
   </si>
   <si>
     <t>FDEE90B15CAD405E463BFF80FD75EF34</t>
@@ -1438,7 +1438,7 @@
     <t>table__Sales.SalesReason.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesReason.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesReason.sql</t>
   </si>
   <si>
     <t>47485D008572AEEFECB84EE3E0F1DE6E</t>
@@ -1450,7 +1450,7 @@
     <t>table__Sales.SalesTaxRate.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesTaxRate.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesTaxRate.sql</t>
   </si>
   <si>
     <t>32719803958AC6D18D90AA966A22B082</t>
@@ -1462,7 +1462,7 @@
     <t>table__Sales.SalesTerritory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesTerritory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesTerritory.sql</t>
   </si>
   <si>
     <t>B790E7EFC56E9AC828FFDE5038CFADB6</t>
@@ -1474,7 +1474,7 @@
     <t>table__Sales.SalesTerritoryHistory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SalesTerritoryHistory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesTerritoryHistory.sql</t>
   </si>
   <si>
     <t>1244394A085CB4B94173FDD051942941</t>
@@ -1486,7 +1486,7 @@
     <t>table__Sales.ShoppingCartItem.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.ShoppingCartItem.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.ShoppingCartItem.sql</t>
   </si>
   <si>
     <t>9EE4E094750CB2905440942505351ADA</t>
@@ -1498,7 +1498,7 @@
     <t>table__Sales.SpecialOffer.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SpecialOffer.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SpecialOffer.sql</t>
   </si>
   <si>
     <t>F34B35578D75C869E165D90095D3E093</t>
@@ -1510,7 +1510,7 @@
     <t>table__Sales.SpecialOfferProduct.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.SpecialOfferProduct.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SpecialOfferProduct.sql</t>
   </si>
   <si>
     <t>90353DD5FEA1EE6BC0D43B195EE9727F</t>
@@ -1522,7 +1522,7 @@
     <t>table__Sales.Store.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__Sales.Store.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.Store.sql</t>
   </si>
   <si>
     <t>73C4AAD5EC0DEF9534BCA7A958692CEC</t>
@@ -1534,7 +1534,7 @@
     <t>table__dbo.AWBuildVersion.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__dbo.AWBuildVersion.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__dbo.AWBuildVersion.sql</t>
   </si>
   <si>
     <t>Incorrect Analysis Warning: 1, Total Statement count: 1, Conventional Statement count: 1, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 0, High category breaks: 0</t>
@@ -1549,7 +1549,7 @@
     <t>table__dbo.DatabaseLog.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__dbo.DatabaseLog.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__dbo.DatabaseLog.sql</t>
   </si>
   <si>
     <t>F0343BA0E4E0A37B096257477CFF2588</t>
@@ -1561,7 +1561,7 @@
     <t>table__dbo.ErrorLog.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/table__dbo.ErrorLog.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__dbo.ErrorLog.sql</t>
   </si>
   <si>
     <t>4163DE2662EE1C6C040E46334FE032D2</t>
@@ -1573,7 +1573,7 @@
     <t>view__HumanResources.vEmployee.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vEmployee.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vEmployee.sql</t>
   </si>
   <si>
     <t>CREATE_VIEW</t>
@@ -1588,7 +1588,7 @@
     <t>view__HumanResources.vEmployeeDepartment.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartment.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartment.sql</t>
   </si>
   <si>
     <t>679B2E1E4FFFF228E3C17A5AF6EAB185</t>
@@ -1600,7 +1600,7 @@
     <t>view__HumanResources.vEmployeeDepartmentHistory.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartmentHistory.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartmentHistory.sql</t>
   </si>
   <si>
     <t>50C7657DBE2E158414B1BEE40DE7858D</t>
@@ -1612,7 +1612,7 @@
     <t>view__HumanResources.vJobCandidate.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidate.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidate.sql</t>
   </si>
   <si>
     <t>CREATE_VIEW,UNKNOWN,VAR_DECLARE</t>
@@ -1630,7 +1630,7 @@
     <t>view__HumanResources.vJobCandidateEducation.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEducation.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEducation.sql</t>
   </si>
   <si>
     <t>Incorrect Analysis Warning: 1, Total Statement count: 14, Conventional Statement count: 14, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1645,7 +1645,7 @@
     <t>view__HumanResources.vJobCandidateEmployment.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEmployment.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEmployment.sql</t>
   </si>
   <si>
     <t>Incorrect Analysis Warning: 1, Total Statement count: 12, Conventional Statement count: 12, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1660,7 +1660,7 @@
     <t>view__Person.vAdditionalContactInfo.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Person.vAdditionalContactInfo.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Person.vAdditionalContactInfo.sql</t>
   </si>
   <si>
     <t>Total Statement count: 24, Conventional Statement count: 13, Simple Statement count: 11, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1675,7 +1675,7 @@
     <t>view__Person.vStateProvinceCountryRegion.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Person.vStateProvinceCountryRegion.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Person.vStateProvinceCountryRegion.sql</t>
   </si>
   <si>
     <t>D1B666575C3150FA07161F6E1A8129F0</t>
@@ -1687,7 +1687,7 @@
     <t>view__Production.vProductAndDescription.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Production.vProductAndDescription.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Production.vProductAndDescription.sql</t>
   </si>
   <si>
     <t>AD0C95888E8820742BAA5DE17B3A96AA</t>
@@ -1699,7 +1699,7 @@
     <t>view__Production.vProductModelCatalogDescription.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Production.vProductModelCatalogDescription.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Production.vProductModelCatalogDescription.sql</t>
   </si>
   <si>
     <t>Total Statement count: 32, Conventional Statement count: 22, Simple Statement count: 10, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1714,7 +1714,7 @@
     <t>view__Production.vProductModelInstructions.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Production.vProductModelInstructions.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Production.vProductModelInstructions.sql</t>
   </si>
   <si>
     <t>1A47F8B4BC2B7ACEDB60EE1B1AAD4470</t>
@@ -1726,7 +1726,7 @@
     <t>view__Purchasing.vVendorWithAddresses.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithAddresses.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithAddresses.sql</t>
   </si>
   <si>
     <t>D7CD68F5F89F8956B1DBD51AB75496CB</t>
@@ -1738,7 +1738,7 @@
     <t>view__Purchasing.vVendorWithContacts.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithContacts.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithContacts.sql</t>
   </si>
   <si>
     <t>8FCD0C6976595D45BF4770D9FAA0EC11</t>
@@ -1750,7 +1750,7 @@
     <t>view__Sales.vIndividualCustomer.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vIndividualCustomer.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vIndividualCustomer.sql</t>
   </si>
   <si>
     <t>AA4431CE6421DCB43574B5BCCB8273B5</t>
@@ -1762,7 +1762,7 @@
     <t>view__Sales.vPersonDemographics.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vPersonDemographics.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vPersonDemographics.sql</t>
   </si>
   <si>
     <t>Total Statement count: 14, Conventional Statement count: 14, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1777,7 +1777,7 @@
     <t>view__Sales.vSalesPerson.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vSalesPerson.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vSalesPerson.sql</t>
   </si>
   <si>
     <t>090AE69AE0362DEA70853EFBAE038CE7</t>
@@ -1789,7 +1789,7 @@
     <t>view__Sales.vSalesPersonSalesByFiscalYears.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vSalesPersonSalesByFiscalYears.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vSalesPersonSalesByFiscalYears.sql</t>
   </si>
   <si>
     <t>Total Statement count: 1, Conventional Statement count: 1, Simple Statement count: 0, Pivot functions: 1, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1804,7 +1804,7 @@
     <t>view__Sales.vStoreWithAddresses.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vStoreWithAddresses.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vStoreWithAddresses.sql</t>
   </si>
   <si>
     <t>0AFF094C65B3C3F48B8130C48F8F6294</t>
@@ -1816,7 +1816,7 @@
     <t>view__Sales.vStoreWithContacts.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vStoreWithContacts.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vStoreWithContacts.sql</t>
   </si>
   <si>
     <t>C707BD34FAA1443727F92838D30983B9</t>
@@ -1828,7 +1828,7 @@
     <t>view__Sales.vStoreWithDemographics.sql</t>
   </si>
   <si>
-    <t>D:/autovista/output_lakebridge/_source_export/sql/view__Sales.vStoreWithDemographics.sql</t>
+    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vStoreWithDemographics.sql</t>
   </si>
   <si>
     <t>06140F8E409F58532DAB1C311FA4E9B9</t>
@@ -2047,82 +2047,82 @@
     <t>ISNULL</t>
   </si>
   <si>
+    <t>OPTION</t>
+  </si>
+  <si>
+    <t>COALESCE</t>
+  </si>
+  <si>
     <t>TEXT</t>
   </si>
   <si>
-    <t>COALESCE</t>
-  </si>
-  <si>
-    <t>OPTION</t>
+    <t>ERROR_NUMBER</t>
   </si>
   <si>
     <t>CONTAINSTABLE</t>
   </si>
   <si>
-    <t>ERROR_NUMBER</t>
+    <t>DATEADD</t>
+  </si>
+  <si>
+    <t>RAISERROR</t>
+  </si>
+  <si>
+    <t>ERROR_STATE</t>
+  </si>
+  <si>
+    <t>ERROR_PROCEDURE</t>
+  </si>
+  <si>
+    <t>OF</t>
   </si>
   <si>
     <t>ERROR_MESSAGE</t>
   </si>
   <si>
+    <t>SQL:COLUMN</t>
+  </si>
+  <si>
+    <t>ERROR_SEVERITY</t>
+  </si>
+  <si>
     <t>ERROR_LINE</t>
   </si>
   <si>
-    <t>DATEADD</t>
-  </si>
-  <si>
-    <t>SQL:COLUMN</t>
-  </si>
-  <si>
-    <t>OF</t>
-  </si>
-  <si>
-    <t>ERROR_STATE</t>
-  </si>
-  <si>
-    <t>RAISERROR</t>
-  </si>
-  <si>
-    <t>ERROR_PROCEDURE</t>
-  </si>
-  <si>
-    <t>ERROR_SEVERITY</t>
+    <t>PIVOT</t>
+  </si>
+  <si>
+    <t>XACT_STATE</t>
   </si>
   <si>
     <t>REPLICATE</t>
   </si>
   <si>
+    <t>SERVERPROPERTY</t>
+  </si>
+  <si>
+    <t>DATALENGTH</t>
+  </si>
+  <si>
+    <t>COUNT</t>
+  </si>
+  <si>
+    <t>FREETEXTTABLE</t>
+  </si>
+  <si>
+    <t>YEAR</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>INTO</t>
+  </si>
+  <si>
+    <t>REPLACE</t>
+  </si>
+  <si>
     <t>NUMERIC</t>
-  </si>
-  <si>
-    <t>REPLACE</t>
-  </si>
-  <si>
-    <t>DATALENGTH</t>
-  </si>
-  <si>
-    <t>COUNT</t>
-  </si>
-  <si>
-    <t>SERVERPROPERTY</t>
-  </si>
-  <si>
-    <t>YEAR</t>
-  </si>
-  <si>
-    <t>STRING</t>
-  </si>
-  <si>
-    <t>INTO</t>
-  </si>
-  <si>
-    <t>PIVOT</t>
-  </si>
-  <si>
-    <t>XACT_STATE</t>
-  </si>
-  <si>
-    <t>FREETEXTTABLE</t>
   </si>
   <si>
     <t>Script</t>
@@ -2858,7 +2858,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3573,10 +3573,10 @@
         <v>703</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>704</v>
@@ -5339,7 +5339,7 @@
         <v>153</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>698</v>
@@ -5353,7 +5353,7 @@
         <v>153</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>698</v>
@@ -9154,7 +9154,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="6" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="B21" s="6">
         <v>1</v>
@@ -14864,54 +14864,54 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>574</v>
+        <v>540</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C2" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>246</v>
+        <v>540</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C3" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C4" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>286</v>
+        <v>553</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C5" s="6">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>286</v>
+        <v>212</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -14919,21 +14919,21 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>414</v>
+        <v>212</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
       <c r="C7" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
@@ -14941,32 +14941,32 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>362</v>
+        <v>212</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>663</v>
+        <v>615</v>
       </c>
       <c r="C9" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
-        <v>358</v>
+        <v>212</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="C10" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>189</v>
+        <v>286</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>687</v>
+        <v>664</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -14974,21 +14974,21 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
-        <v>189</v>
+        <v>286</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
       <c r="C12" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -14996,21 +14996,21 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
-        <v>486</v>
+        <v>294</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C14" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
-        <v>402</v>
+        <v>334</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -15018,10 +15018,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
@@ -15029,21 +15029,21 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
-        <v>298</v>
+        <v>486</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C17" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
-        <v>177</v>
+        <v>583</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
@@ -15051,21 +15051,21 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
-        <v>535</v>
+        <v>583</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>663</v>
+        <v>690</v>
       </c>
       <c r="C19" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>535</v>
+        <v>583</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
@@ -15073,10 +15073,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
-        <v>535</v>
+        <v>583</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="C21" s="6">
         <v>1</v>
@@ -15084,10 +15084,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="6" t="s">
-        <v>76</v>
+        <v>583</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
@@ -15095,43 +15095,43 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>76</v>
+        <v>530</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C23" s="6">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>558</v>
+        <v>183</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>690</v>
+        <v>615</v>
       </c>
       <c r="C24" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>558</v>
+        <v>183</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C25" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>558</v>
+        <v>246</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C26" s="6">
         <v>1</v>
@@ -15139,7 +15139,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>663</v>
@@ -15150,21 +15150,21 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>507</v>
+        <v>195</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C28" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C29" s="6">
         <v>1</v>
@@ -15172,21 +15172,21 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C30" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="6" t="s">
-        <v>254</v>
+        <v>153</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C31" s="6">
         <v>1</v>
@@ -15194,43 +15194,43 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="6" t="s">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>615</v>
+        <v>686</v>
       </c>
       <c r="C32" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>666</v>
+        <v>689</v>
       </c>
       <c r="C33" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
-        <v>474</v>
+        <v>153</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C34" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>290</v>
+        <v>165</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="C35" s="6">
         <v>1</v>
@@ -15238,21 +15238,21 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>503</v>
+        <v>128</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C36" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>100</v>
+        <v>278</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>686</v>
+        <v>663</v>
       </c>
       <c r="C37" s="6">
         <v>1</v>
@@ -15260,32 +15260,32 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="6" t="s">
-        <v>100</v>
+        <v>218</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>665</v>
+        <v>615</v>
       </c>
       <c r="C38" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
-        <v>100</v>
+        <v>218</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="C39" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
-        <v>165</v>
+        <v>386</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="C40" s="6">
         <v>1</v>
@@ -15293,32 +15293,32 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C41" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="6" t="s">
-        <v>426</v>
+        <v>596</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C42" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="6" t="s">
-        <v>206</v>
+        <v>76</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>615</v>
+        <v>670</v>
       </c>
       <c r="C43" s="6">
         <v>1</v>
@@ -15326,10 +15326,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="6" t="s">
-        <v>294</v>
+        <v>76</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C44" s="6">
         <v>1</v>
@@ -15337,10 +15337,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="6" t="s">
-        <v>382</v>
+        <v>132</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="C45" s="6">
         <v>1</v>
@@ -15348,21 +15348,21 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="6" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C46" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="6" t="s">
-        <v>430</v>
+        <v>140</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C47" s="6">
         <v>1</v>
@@ -15370,10 +15370,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="6" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="C48" s="6">
         <v>1</v>
@@ -15381,10 +15381,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="6" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="C49" s="6">
         <v>1</v>
@@ -15392,10 +15392,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="6" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -15403,10 +15403,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="6" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C51" s="6">
         <v>1</v>
@@ -15414,43 +15414,43 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="6" t="s">
-        <v>370</v>
+        <v>140</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="C52" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="6" t="s">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="C53" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="6" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>615</v>
+        <v>684</v>
       </c>
       <c r="C54" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="6" t="s">
-        <v>171</v>
+        <v>100</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C55" s="6">
         <v>1</v>
@@ -15458,10 +15458,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="6" t="s">
-        <v>310</v>
+        <v>100</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C56" s="6">
         <v>1</v>
@@ -15469,21 +15469,21 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="6" t="s">
-        <v>310</v>
+        <v>100</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>663</v>
+        <v>687</v>
       </c>
       <c r="C57" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="6" t="s">
-        <v>302</v>
+        <v>254</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C58" s="6">
         <v>1</v>
@@ -15491,32 +15491,32 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="6" t="s">
-        <v>322</v>
+        <v>51</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C59" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="6" t="s">
-        <v>322</v>
+        <v>51</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="C60" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="6" t="s">
-        <v>70</v>
+        <v>382</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C61" s="6">
         <v>1</v>
@@ -15524,10 +15524,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="6" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -15535,10 +15535,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="6" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C63" s="6">
         <v>2</v>
@@ -15546,32 +15546,32 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="6" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>615</v>
+        <v>669</v>
       </c>
       <c r="C64" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="6" t="s">
-        <v>201</v>
+        <v>503</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C65" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="6" t="s">
-        <v>136</v>
+        <v>342</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -15579,87 +15579,87 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="6" t="s">
-        <v>136</v>
+        <v>274</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C67" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="6" t="s">
-        <v>136</v>
+        <v>402</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C68" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="6" t="s">
-        <v>212</v>
+        <v>270</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="C69" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="6" t="s">
-        <v>212</v>
+        <v>370</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C70" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="6" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="C71" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="6" t="s">
-        <v>212</v>
+        <v>574</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="C72" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="6" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>667</v>
+        <v>615</v>
       </c>
       <c r="C73" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="6" t="s">
-        <v>494</v>
+        <v>201</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -15667,18 +15667,18 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="6" t="s">
-        <v>446</v>
+        <v>201</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="C75" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="6" t="s">
-        <v>446</v>
+        <v>498</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>663</v>
@@ -15689,21 +15689,21 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="6" t="s">
-        <v>153</v>
+        <v>306</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="C77" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="6" t="s">
-        <v>153</v>
+        <v>306</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="C78" s="6">
         <v>1</v>
@@ -15711,10 +15711,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="6" t="s">
-        <v>153</v>
+        <v>302</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C79" s="6">
         <v>1</v>
@@ -15722,7 +15722,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="6" t="s">
-        <v>153</v>
+        <v>390</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>663</v>
@@ -15733,10 +15733,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="6" t="s">
-        <v>153</v>
+        <v>390</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>694</v>
+        <v>664</v>
       </c>
       <c r="C81" s="6">
         <v>1</v>
@@ -15744,43 +15744,43 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="6" t="s">
-        <v>224</v>
+        <v>494</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C82" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="6" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C83" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="6" t="s">
-        <v>466</v>
+        <v>535</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C84" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="6" t="s">
-        <v>128</v>
+        <v>535</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>671</v>
+        <v>693</v>
       </c>
       <c r="C85" s="6">
         <v>1</v>
@@ -15788,10 +15788,10 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="6" t="s">
-        <v>274</v>
+        <v>171</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>663</v>
+        <v>615</v>
       </c>
       <c r="C86" s="6">
         <v>2</v>
@@ -15799,10 +15799,10 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="6" t="s">
-        <v>390</v>
+        <v>171</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="C87" s="6">
         <v>1</v>
@@ -15810,7 +15810,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="6" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>663</v>
@@ -15821,10 +15821,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="6" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C89" s="6">
         <v>2</v>
@@ -15843,21 +15843,21 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="6" t="s">
-        <v>583</v>
+        <v>230</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>692</v>
+        <v>664</v>
       </c>
       <c r="C91" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="6" t="s">
-        <v>583</v>
+        <v>310</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>689</v>
+        <v>664</v>
       </c>
       <c r="C92" s="6">
         <v>1</v>
@@ -15865,32 +15865,32 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="6" t="s">
-        <v>583</v>
+        <v>310</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="C93" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="6" t="s">
-        <v>583</v>
+        <v>418</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C94" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="6" t="s">
-        <v>583</v>
+        <v>206</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>666</v>
+        <v>615</v>
       </c>
       <c r="C95" s="6">
         <v>1</v>
@@ -15898,21 +15898,21 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="6" t="s">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C96" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="6" t="s">
-        <v>94</v>
+        <v>482</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C97" s="6">
         <v>1</v>
@@ -15920,10 +15920,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="6" t="s">
-        <v>318</v>
+        <v>70</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C98" s="6">
         <v>1</v>
@@ -15931,10 +15931,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="6" t="s">
-        <v>374</v>
+        <v>70</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="C99" s="6">
         <v>1</v>
@@ -15942,32 +15942,32 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="6" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C100" s="6">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="6" t="s">
-        <v>450</v>
+        <v>147</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="C101" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="6" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="C102" s="6">
         <v>1</v>
@@ -15975,10 +15975,10 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="6" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C103" s="6">
         <v>1</v>
@@ -15986,21 +15986,21 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="6" t="s">
-        <v>418</v>
+        <v>147</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="C104" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="6" t="s">
-        <v>422</v>
+        <v>147</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="C105" s="6">
         <v>1</v>
@@ -16008,10 +16008,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="6" t="s">
-        <v>422</v>
+        <v>147</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="C106" s="6">
         <v>1</v>
@@ -16019,21 +16019,21 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="6" t="s">
-        <v>498</v>
+        <v>147</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C107" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="6" t="s">
-        <v>378</v>
+        <v>147</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>663</v>
+        <v>676</v>
       </c>
       <c r="C108" s="6">
         <v>1</v>
@@ -16041,10 +16041,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="6" t="s">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C109" s="6">
         <v>1</v>
@@ -16052,21 +16052,21 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="6" t="s">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C110" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="6" t="s">
-        <v>122</v>
+        <v>430</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C111" s="6">
         <v>1</v>
@@ -16074,7 +16074,7 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="6" t="s">
-        <v>278</v>
+        <v>430</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>663</v>
@@ -16085,32 +16085,32 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="6" t="s">
-        <v>540</v>
+        <v>466</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C113" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="6" t="s">
-        <v>540</v>
+        <v>298</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C114" s="6">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="6" t="s">
-        <v>342</v>
+        <v>298</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C115" s="6">
         <v>1</v>
@@ -16118,21 +16118,21 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="6" t="s">
-        <v>140</v>
+        <v>524</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="6" t="s">
-        <v>140</v>
+        <v>558</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="C117" s="6">
         <v>1</v>
@@ -16140,10 +16140,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="6" t="s">
-        <v>140</v>
+        <v>558</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="C118" s="6">
         <v>1</v>
@@ -16151,32 +16151,32 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="6" t="s">
-        <v>140</v>
+        <v>558</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>682</v>
+        <v>663</v>
       </c>
       <c r="C119" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="6" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="C120" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="6" t="s">
-        <v>140</v>
+        <v>318</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="C121" s="6">
         <v>1</v>
@@ -16184,10 +16184,10 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="6" t="s">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C122" s="6">
         <v>1</v>
@@ -16195,43 +16195,43 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="6" t="s">
-        <v>140</v>
+        <v>434</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>693</v>
+        <v>664</v>
       </c>
       <c r="C123" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="6" t="s">
-        <v>553</v>
+        <v>94</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C124" s="6">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="6" t="s">
-        <v>596</v>
+        <v>446</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>663</v>
+        <v>694</v>
       </c>
       <c r="C125" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="6" t="s">
-        <v>147</v>
+        <v>446</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>682</v>
+        <v>663</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -16239,10 +16239,10 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="6" t="s">
-        <v>147</v>
+        <v>378</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
       <c r="C127" s="6">
         <v>1</v>
@@ -16250,54 +16250,54 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="6" t="s">
-        <v>147</v>
+        <v>322</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C128" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="6" t="s">
-        <v>147</v>
+        <v>322</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="C129" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="6" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C130" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="6" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="C131" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="6" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -16305,32 +16305,32 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="6" t="s">
-        <v>147</v>
+        <v>474</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C133" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="6" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>615</v>
+        <v>688</v>
       </c>
       <c r="C134" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="6" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="C135" s="6">
         <v>1</v>
@@ -16338,10 +16338,10 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="6" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -16349,10 +16349,10 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="6" t="s">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C137" s="6">
         <v>1</v>
@@ -16360,10 +16360,10 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="6" t="s">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -16371,13 +16371,13 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="6" t="s">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C139" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -16500,15 +16500,18 @@
     </row>
     <row r="2" spans="1:34">
       <c r="A2" s="6" t="s">
-        <v>574</v>
+        <v>540</v>
       </c>
       <c r="B2" s="6">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="K2" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:34">
       <c r="A3" s="6" t="s">
-        <v>246</v>
+        <v>414</v>
       </c>
       <c r="B3" s="6">
         <v>1</v>
@@ -16516,435 +16519,456 @@
     </row>
     <row r="4" spans="1:34">
       <c r="A4" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="C4" s="6">
-        <v>2</v>
+        <v>553</v>
+      </c>
+      <c r="B4" s="6">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:34">
       <c r="A5" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="B5" s="6">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
+        <v>212</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+      <c r="R5" s="6">
+        <v>2</v>
+      </c>
+      <c r="T5" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:34">
       <c r="A6" s="6" t="s">
-        <v>414</v>
+        <v>286</v>
       </c>
       <c r="B6" s="6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:34">
       <c r="A7" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="6">
+        <v>470</v>
+      </c>
+      <c r="B7" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:34">
       <c r="A8" s="6" t="s">
-        <v>362</v>
+        <v>294</v>
       </c>
       <c r="B8" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:34">
       <c r="A9" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="C9" s="6">
+        <v>334</v>
+      </c>
+      <c r="B9" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:34">
       <c r="A10" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="T10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="6">
+        <v>290</v>
+      </c>
+      <c r="B10" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:34">
       <c r="A11" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1</v>
+        <v>486</v>
+      </c>
+      <c r="B11" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:34">
       <c r="A12" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="B12" s="6">
-        <v>3</v>
+        <v>583</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="J12" s="6">
+        <v>1</v>
+      </c>
+      <c r="N12" s="6">
+        <v>1</v>
+      </c>
+      <c r="W12" s="6">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:34">
       <c r="A13" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1</v>
+        <v>530</v>
+      </c>
+      <c r="B13" s="6">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:34">
       <c r="A14" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="B14" s="6">
+        <v>183</v>
+      </c>
+      <c r="D14" s="6">
         <v>2</v>
       </c>
-      <c r="C14" s="6">
+      <c r="G14" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:34">
       <c r="A15" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="G15" s="6">
+        <v>246</v>
+      </c>
+      <c r="B15" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:34">
       <c r="A16" s="6" t="s">
-        <v>535</v>
+        <v>326</v>
       </c>
       <c r="B16" s="6">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F17" s="6">
+        <v>1</v>
+      </c>
+      <c r="G17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
+      <c r="A18" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1</v>
+      </c>
+      <c r="M18" s="6">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
+      <c r="A19" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="O19" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
+      <c r="A20" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
+      <c r="A21" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
+      <c r="A22" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="6">
+        <v>2</v>
+      </c>
+      <c r="F22" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
+      <c r="A23" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
+      <c r="A24" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B24" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
+      <c r="A25" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="B25" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
+      <c r="A26" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="6">
-        <v>1</v>
-      </c>
-      <c r="J17" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30">
-      <c r="A18" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="B18" s="6">
+      <c r="E26" s="6">
+        <v>1</v>
+      </c>
+      <c r="J26" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
+      <c r="A27" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I27" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
+      <c r="A28" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B28" s="6">
         <v>2</v>
       </c>
-      <c r="I18" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30">
-      <c r="A19" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="B19" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30">
-      <c r="A20" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="B20" s="6">
+    </row>
+    <row r="29" spans="1:29">
+      <c r="A29" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1</v>
+      </c>
+      <c r="L29" s="6">
+        <v>2</v>
+      </c>
+      <c r="P29" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>1</v>
+      </c>
+      <c r="S29" s="6">
+        <v>1</v>
+      </c>
+      <c r="U29" s="6">
+        <v>1</v>
+      </c>
+      <c r="V29" s="6">
+        <v>1</v>
+      </c>
+      <c r="X29" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
+      <c r="A30" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
+      <c r="A31" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B31" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
+      <c r="A32" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="6">
+        <v>1</v>
+      </c>
+      <c r="N32" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C33" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" s="6">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6">
+        <v>2</v>
+      </c>
+      <c r="I34" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="B35" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="B36" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B37" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B39" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B40" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:30">
-      <c r="A21" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B21" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30">
-      <c r="A22" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K22" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30">
-      <c r="A23" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B23" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30">
-      <c r="A24" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D24" s="6">
-        <v>2</v>
-      </c>
-      <c r="F24" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30">
-      <c r="A25" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="B25" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30">
-      <c r="A26" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="B26" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30">
-      <c r="A27" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="B27" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30">
-      <c r="A28" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" s="6">
-        <v>1</v>
-      </c>
-      <c r="W28" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30">
-      <c r="A29" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="T29" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30">
-      <c r="A30" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B30" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30">
-      <c r="A31" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="B31" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30">
-      <c r="A32" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31">
-      <c r="A33" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="B33" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31">
-      <c r="A34" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="C34" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31">
-      <c r="A35" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="B35" s="6">
-        <v>1</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31">
-      <c r="A36" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F36" s="6">
-        <v>1</v>
-      </c>
-      <c r="G36" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31">
-      <c r="A37" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="6">
-        <v>1</v>
-      </c>
-      <c r="P37" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31">
-      <c r="A38" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="B38" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:31">
-      <c r="A39" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="B39" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:31">
-      <c r="A40" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D40" s="6">
-        <v>2</v>
-      </c>
-      <c r="AE40" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31">
+    <row r="41" spans="1:9">
       <c r="A41" s="6" t="s">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="B41" s="6">
         <v>4</v>
       </c>
-      <c r="C41" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:31">
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="B42" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D43" s="6">
+        <v>3</v>
+      </c>
+      <c r="F43" s="6">
+        <v>1</v>
+      </c>
+      <c r="G43" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="B44" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B45" s="6">
+        <v>1</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="C42" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31">
-      <c r="A43" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B43" s="6">
-        <v>4</v>
-      </c>
-      <c r="C43" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31">
-      <c r="A44" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" s="6">
-        <v>1</v>
-      </c>
-      <c r="J44" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31">
-      <c r="A45" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D45" s="6">
-        <v>3</v>
-      </c>
-      <c r="F45" s="6">
-        <v>1</v>
-      </c>
-      <c r="G45" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:31">
-      <c r="A46" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F46" s="6">
-        <v>1</v>
-      </c>
-      <c r="H46" s="6">
-        <v>2</v>
-      </c>
-      <c r="K46" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:31">
+      <c r="C46" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D47" s="6">
-        <v>4</v>
-      </c>
-      <c r="F47" s="6">
-        <v>1</v>
-      </c>
-      <c r="G47" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q47" s="6">
-        <v>2</v>
-      </c>
-      <c r="R47" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:31">
+        <v>390</v>
+      </c>
+      <c r="B47" s="6">
+        <v>1</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="6" t="s">
         <v>494</v>
       </c>
@@ -16952,364 +16976,340 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:34">
+    <row r="49" spans="1:33">
       <c r="A49" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="B49" s="6">
+        <v>10</v>
+      </c>
+      <c r="E49" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG49" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33">
+      <c r="A50" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33">
+      <c r="A51" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B51" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33">
+      <c r="A52" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B52" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33">
+      <c r="A53" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B53" s="6">
+        <v>3</v>
+      </c>
+      <c r="C53" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33">
+      <c r="A54" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B54" s="6">
+        <v>4</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33">
+      <c r="A55" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B55" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33">
+      <c r="A56" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33">
+      <c r="A57" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="B57" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33">
+      <c r="A58" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B58" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33">
+      <c r="A59" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="6">
+        <v>1</v>
+      </c>
+      <c r="J59" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:33">
+      <c r="A60" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B60" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33">
+      <c r="A61" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E61" s="6">
+        <v>4</v>
+      </c>
+      <c r="H61" s="6">
+        <v>1</v>
+      </c>
+      <c r="L61" s="6">
+        <v>1</v>
+      </c>
+      <c r="P61" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>1</v>
+      </c>
+      <c r="S61" s="6">
+        <v>1</v>
+      </c>
+      <c r="U61" s="6">
+        <v>1</v>
+      </c>
+      <c r="V61" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33">
+      <c r="A62" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B62" s="6">
+        <v>1</v>
+      </c>
+      <c r="C62" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:33">
+      <c r="A63" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B63" s="6">
+        <v>1</v>
+      </c>
+      <c r="C63" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33">
+      <c r="A64" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B64" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:34">
+      <c r="A65" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B65" s="6">
+        <v>2</v>
+      </c>
+      <c r="C65" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:34">
+      <c r="A66" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B66" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:34">
+      <c r="A67" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="B67" s="6">
+        <v>2</v>
+      </c>
+      <c r="K67" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE67" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:34">
+      <c r="A68" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E68" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:34">
+      <c r="A69" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B69" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:34">
+      <c r="A70" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B70" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:34">
+      <c r="A71" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C71" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:34">
+      <c r="A72" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F72" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:34">
+      <c r="A73" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="B49" s="6">
-        <v>1</v>
-      </c>
-      <c r="X49" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:34">
-      <c r="A50" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B50" s="6">
-        <v>1</v>
-      </c>
-      <c r="E50" s="6">
-        <v>1</v>
-      </c>
-      <c r="L50" s="6">
+      <c r="B73" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH73" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:34">
+      <c r="A74" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B74" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:34">
+      <c r="A75" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B75" s="6">
+        <v>4</v>
+      </c>
+      <c r="C75" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:34">
+      <c r="A76" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F76" s="6">
+        <v>1</v>
+      </c>
+      <c r="H76" s="6">
+        <v>2</v>
+      </c>
+      <c r="I76" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:34">
+      <c r="A77" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B77" s="6">
         <v>3</v>
       </c>
-      <c r="AB50" s="6">
-        <v>1</v>
-      </c>
-      <c r="AH50" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:34">
-      <c r="A51" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="B51" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:34">
-      <c r="A52" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="B52" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:34">
-      <c r="A53" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="B53" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:34">
-      <c r="A54" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="K54" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:34">
-      <c r="A55" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B55" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:34">
-      <c r="A56" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="B56" s="6">
-        <v>1</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:34">
-      <c r="A57" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B57" s="6">
-        <v>3</v>
-      </c>
-      <c r="C57" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:34">
-      <c r="A58" s="6" t="s">
-        <v>583</v>
-      </c>
-      <c r="F58" s="6">
-        <v>1</v>
-      </c>
-      <c r="J58" s="6">
-        <v>1</v>
-      </c>
-      <c r="P58" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC58" s="6">
-        <v>1</v>
-      </c>
-      <c r="AF58" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:34">
-      <c r="A59" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="B59" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:34">
-      <c r="A60" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F60" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:34">
-      <c r="A61" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B61" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:34">
-      <c r="A62" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="B62" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:34">
-      <c r="A63" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="B63" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:34">
-      <c r="A64" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="B64" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:33">
-      <c r="A65" s="6" t="s">
+    </row>
+    <row r="78" spans="1:34">
+      <c r="A78" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="O78" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB78" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:34">
+      <c r="A79" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C79" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:34">
+      <c r="A80" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E65" s="6">
-        <v>1</v>
-      </c>
-      <c r="J65" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:33">
-      <c r="A66" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="B66" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:33">
-      <c r="A67" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B67" s="6">
-        <v>1</v>
-      </c>
-      <c r="C67" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:33">
-      <c r="A68" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="B68" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:33">
-      <c r="A69" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="B69" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:33">
-      <c r="A70" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F70" s="6">
-        <v>1</v>
-      </c>
-      <c r="H70" s="6">
-        <v>2</v>
-      </c>
-      <c r="K70" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:33">
-      <c r="A71" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B71" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:33">
-      <c r="A72" s="6" t="s">
-        <v>540</v>
-      </c>
-      <c r="B72" s="6">
-        <v>11</v>
-      </c>
-      <c r="I72" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:33">
-      <c r="A73" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="B73" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:33">
-      <c r="A74" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E74" s="6">
-        <v>1</v>
-      </c>
-      <c r="M74" s="6">
-        <v>2</v>
-      </c>
-      <c r="N74" s="6">
-        <v>1</v>
-      </c>
-      <c r="O74" s="6">
-        <v>1</v>
-      </c>
-      <c r="S74" s="6">
-        <v>1</v>
-      </c>
-      <c r="U74" s="6">
-        <v>1</v>
-      </c>
-      <c r="V74" s="6">
-        <v>1</v>
-      </c>
-      <c r="AG74" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:33">
-      <c r="A75" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="B75" s="6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" spans="1:33">
-      <c r="A76" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="B76" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:33">
-      <c r="A77" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E77" s="6">
-        <v>4</v>
-      </c>
-      <c r="H77" s="6">
-        <v>1</v>
-      </c>
-      <c r="M77" s="6">
-        <v>1</v>
-      </c>
-      <c r="N77" s="6">
-        <v>1</v>
-      </c>
-      <c r="O77" s="6">
-        <v>1</v>
-      </c>
-      <c r="S77" s="6">
-        <v>1</v>
-      </c>
-      <c r="U77" s="6">
-        <v>1</v>
-      </c>
-      <c r="V77" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:33">
-      <c r="A78" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D78" s="6">
-        <v>2</v>
-      </c>
-      <c r="G78" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:33">
-      <c r="A79" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="B79" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:33">
-      <c r="A80" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="B80" s="6">
-        <v>1</v>
-      </c>
-      <c r="C80" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+      <c r="E80" s="6">
+        <v>1</v>
+      </c>
+      <c r="J80" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B81" s="6">
-        <v>4</v>
+        <v>177</v>
+      </c>
+      <c r="G81" s="6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -17359,7 +17359,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C3" s="8">
         <v>3</v>
@@ -17367,7 +17367,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C4" s="8">
         <v>1</v>

--- a/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.xlsx
+++ b/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="897">
   <si>
-    <t>Run date/time: 2026-07-07 11:16:22</t>
+    <t>Run date/time: 2026-07-07 20:47:47</t>
   </si>
   <si>
     <t>Code Base Details</t>
@@ -124,7 +124,7 @@
     <t>-d</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql</t>
   </si>
   <si>
     <t>-e</t>
@@ -133,13 +133,13 @@
     <t>-j</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.json</t>
+    <t>D:\autovista_clean\output_lakebridge\reports\lakebridge_report_MS_SQL_Server.json</t>
   </si>
   <si>
     <t>-r</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/reports/lakebridge_report_MS_SQL_Server.xlsx</t>
+    <t>D:\autovista_clean\output_lakebridge\reports\lakebridge_report_MS_SQL_Server.xlsx</t>
   </si>
   <si>
     <t>-t</t>
@@ -151,7 +151,7 @@
     <t>Analyzer run duration:</t>
   </si>
   <si>
-    <t>0h, 0m, 1s</t>
+    <t>0h, 0m, 3s</t>
   </si>
   <si>
     <t>Program Name</t>
@@ -193,7 +193,7 @@
     <t>sql_scalar_function__dbo.ufnGetAccountingEndDate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingEndDate.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingEndDate.sql</t>
   </si>
   <si>
     <t>YES</t>
@@ -220,7 +220,7 @@
     <t>sql_scalar_function__dbo.ufnGetAccountingStartDate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingStartDate.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetAccountingStartDate.sql</t>
   </si>
   <si>
     <t>BAF6458A7E562903BA94D801522005A0</t>
@@ -232,7 +232,7 @@
     <t>sql_scalar_function__dbo.ufnGetDocumentStatusText.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetDocumentStatusText.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetDocumentStatusText.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -250,7 +250,7 @@
     <t>sql_scalar_function__dbo.ufnGetProductDealerPrice.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductDealerPrice.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductDealerPrice.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,SELECT_VAR_ASSIGNMENT,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -268,7 +268,7 @@
     <t>sql_scalar_function__dbo.ufnGetProductListPrice.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductListPrice.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductListPrice.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,SELECT_VAR_ASSIGNMENT,UNKNOWN,VAR_DECLARE</t>
@@ -286,7 +286,7 @@
     <t>sql_scalar_function__dbo.ufnGetProductStandardCost.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductStandardCost.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetProductStandardCost.sql</t>
   </si>
   <si>
     <t>8F43C9F49781DB147EE70E52AF3E8C18</t>
@@ -298,7 +298,7 @@
     <t>sql_scalar_function__dbo.ufnGetPurchaseOrderStatusText.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetPurchaseOrderStatusText.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetPurchaseOrderStatusText.sql</t>
   </si>
   <si>
     <t>65A240477CA9503CB1F2D199C2B26A96</t>
@@ -310,7 +310,7 @@
     <t>sql_scalar_function__dbo.ufnGetSalesOrderStatusText.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetSalesOrderStatusText.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetSalesOrderStatusText.sql</t>
   </si>
   <si>
     <t>0B4FB00504955E9B32739F20AE320DF0</t>
@@ -322,7 +322,7 @@
     <t>sql_scalar_function__dbo.ufnGetStock.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetStock.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnGetStock.sql</t>
   </si>
   <si>
     <t>IF_START,PROGRAM_DECLARATION,SELECT_VAR_ASSIGNMENT,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -340,7 +340,7 @@
     <t>sql_scalar_function__dbo.ufnLeadingZeros.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnLeadingZeros.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_scalar_function__dbo.ufnLeadingZeros.sql</t>
   </si>
   <si>
     <t>PROGRAM_DECLARATION,RETURN,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -358,7 +358,7 @@
     <t>sql_stored_procedure__HumanResources.uspUpdateEmployeeHireInfo.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeHireInfo.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeHireInfo.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,DYNAMIC_SQL,IF_START,INSERT_INTO,UNKNOWN,UPDATE</t>
@@ -376,7 +376,7 @@
     <t>sql_stored_procedure__HumanResources.uspUpdateEmployeeLogin.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeLogin.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeeLogin.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,DYNAMIC_SQL,UNKNOWN,UPDATE</t>
@@ -394,7 +394,7 @@
     <t>sql_stored_procedure__HumanResources.uspUpdateEmployeePersonalInfo.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeePersonalInfo.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_stored_procedure__HumanResources.uspUpdateEmployeePersonalInfo.sql</t>
   </si>
   <si>
     <t>1150510C0F295A53ABB21132050E1842</t>
@@ -406,7 +406,7 @@
     <t>sql_stored_procedure__dbo.uspGetBillOfMaterials.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetBillOfMaterials.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetBillOfMaterials.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,WITH</t>
@@ -424,7 +424,7 @@
     <t>sql_stored_procedure__dbo.uspGetEmployeeManagers.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetEmployeeManagers.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetEmployeeManagers.sql</t>
   </si>
   <si>
     <t>2D5E9F29ED5FDBF0970D8E1DEB7EF7EF</t>
@@ -436,7 +436,7 @@
     <t>sql_stored_procedure__dbo.uspGetManagerEmployees.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetManagerEmployees.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetManagerEmployees.sql</t>
   </si>
   <si>
     <t>8B11ABC3F784D412FED8C567819B2188</t>
@@ -448,7 +448,7 @@
     <t>sql_stored_procedure__dbo.uspGetWhereUsedProductID.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetWhereUsedProductID.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspGetWhereUsedProductID.sql</t>
   </si>
   <si>
     <t>8FFD5EAF979D3F33C7B8447189E5CC10</t>
@@ -460,7 +460,7 @@
     <t>sql_stored_procedure__dbo.uspLogError.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspLogError.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspLogError.sql</t>
   </si>
   <si>
     <t>MEDIUM</t>
@@ -481,7 +481,7 @@
     <t>sql_stored_procedure__dbo.uspPrintError.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspPrintError.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspPrintError.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,UNKNOWN</t>
@@ -499,7 +499,7 @@
     <t>sql_stored_procedure__dbo.uspSearchCandidateResumes.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspSearchCandidateResumes.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_stored_procedure__dbo.uspSearchCandidateResumes.sql</t>
   </si>
   <si>
     <t>CREATE_PROCEDURE,DYNAMIC_SQL,ELSE_IF,IF_START,SELECT_VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -517,7 +517,7 @@
     <t>sql_table_valued_function__dbo.ufnGetContactInformation.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_table_valued_function__dbo.ufnGetContactInformation.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_table_valued_function__dbo.ufnGetContactInformation.sql</t>
   </si>
   <si>
     <t>IF_START,INSERT_INTO,PROGRAM_DECLARATION,UNKNOWN</t>
@@ -535,7 +535,7 @@
     <t>sql_trigger__HumanResources.dEmployee.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__HumanResources.dEmployee.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_trigger__HumanResources.dEmployee.sql</t>
   </si>
   <si>
     <t>DELETE,FOR,IF_START,SET,TRIGGER,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -553,7 +553,7 @@
     <t>sql_trigger__Person.iuPerson.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Person.iuPerson.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_trigger__Person.iuPerson.sql</t>
   </si>
   <si>
     <t>FOR,IF_START,INSERT,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -571,7 +571,7 @@
     <t>sql_trigger__Production.iWorkOrder.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Production.iWorkOrder.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_trigger__Production.iWorkOrder.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,INSERT,INSERT_INTO,SET,TRIGGER,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -589,7 +589,7 @@
     <t>sql_trigger__Production.uWorkOrder.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Production.uWorkOrder.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_trigger__Production.uWorkOrder.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,INSERT_INTO,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -607,7 +607,7 @@
     <t>sql_trigger__Purchasing.dVendor.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.dVendor.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.dVendor.sql</t>
   </si>
   <si>
     <t>DELETE,DYNAMIC_SQL,FOR,IF_START,SELECT_VAR_ASSIGNMENT,SET,TRIGGER,UNKNOWN,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -625,7 +625,7 @@
     <t>sql_trigger__Purchasing.iPurchaseOrderDetail.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.iPurchaseOrderDetail.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.iPurchaseOrderDetail.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,INSERT,INSERT_INTO,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -643,7 +643,7 @@
     <t>sql_trigger__Purchasing.uPurchaseOrderDetail.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderDetail.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderDetail.sql</t>
   </si>
   <si>
     <t>Total Statement count: 22, Conventional Statement count: 14, Simple Statement count: 8, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -658,7 +658,7 @@
     <t>sql_trigger__Purchasing.uPurchaseOrderHeader.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderHeader.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_trigger__Purchasing.uPurchaseOrderHeader.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,IF_START,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -676,7 +676,7 @@
     <t>sql_trigger__Sales.iduSalesOrderDetail.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Sales.iduSalesOrderDetail.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_trigger__Sales.iduSalesOrderDetail.sql</t>
   </si>
   <si>
     <t>DELETE,DYNAMIC_SQL,IF_START,INSERT_INTO,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -694,7 +694,7 @@
     <t>sql_trigger__Sales.uSalesOrderHeader.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/sql_trigger__Sales.uSalesOrderHeader.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/sql_trigger__Sales.uSalesOrderHeader.sql</t>
   </si>
   <si>
     <t>DYNAMIC_SQL,FOR,IF_START,SET,TRIGGER,UNKNOWN,UPDATE,VAR_ASSIGNMENT,VAR_DECLARE</t>
@@ -712,7 +712,7 @@
     <t>table__HumanResources.Department.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.Department.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__HumanResources.Department.sql</t>
   </si>
   <si>
     <t>TABLE_DDL</t>
@@ -730,7 +730,7 @@
     <t>table__HumanResources.Employee.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.Employee.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__HumanResources.Employee.sql</t>
   </si>
   <si>
     <t>A09D1501EFF964FC7F93C28EF51C360A</t>
@@ -742,7 +742,7 @@
     <t>table__HumanResources.EmployeeDepartmentHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.EmployeeDepartmentHistory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__HumanResources.EmployeeDepartmentHistory.sql</t>
   </si>
   <si>
     <t>9228830EC44A62F7A7D2C8F41850032F</t>
@@ -754,7 +754,7 @@
     <t>table__HumanResources.EmployeePayHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.EmployeePayHistory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__HumanResources.EmployeePayHistory.sql</t>
   </si>
   <si>
     <t>42D4CA98D5026067D7084C89A9AF12B6</t>
@@ -766,7 +766,7 @@
     <t>table__HumanResources.JobCandidate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.JobCandidate.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__HumanResources.JobCandidate.sql</t>
   </si>
   <si>
     <t>D678671C1A1D596D2DFB28AF39E3DBBC</t>
@@ -778,7 +778,7 @@
     <t>table__HumanResources.Shift.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__HumanResources.Shift.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__HumanResources.Shift.sql</t>
   </si>
   <si>
     <t>0839B989DA5FCAF2B2737EBC540D47FA</t>
@@ -790,7 +790,7 @@
     <t>table__Person.Address.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.Address.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.Address.sql</t>
   </si>
   <si>
     <t>485B09A2BAF22C3CD474D91BB496DDA3</t>
@@ -802,7 +802,7 @@
     <t>table__Person.AddressType.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.AddressType.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.AddressType.sql</t>
   </si>
   <si>
     <t>08B4363009B611557F05C437003C683F</t>
@@ -814,7 +814,7 @@
     <t>table__Person.BusinessEntity.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.BusinessEntity.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.BusinessEntity.sql</t>
   </si>
   <si>
     <t>9A22940EBB8A151E20E568F9C55DF1AE</t>
@@ -826,7 +826,7 @@
     <t>table__Person.BusinessEntityAddress.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.BusinessEntityAddress.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.BusinessEntityAddress.sql</t>
   </si>
   <si>
     <t>526B5BBA957622BBC2F5259A809EACD6</t>
@@ -838,7 +838,7 @@
     <t>table__Person.BusinessEntityContact.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.BusinessEntityContact.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.BusinessEntityContact.sql</t>
   </si>
   <si>
     <t>5B8957D0AC73C90AB40E85FBA5364190</t>
@@ -850,7 +850,7 @@
     <t>table__Person.ContactType.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.ContactType.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.ContactType.sql</t>
   </si>
   <si>
     <t>5E5B91699E103EB7CFF0FCB8160603BA</t>
@@ -862,7 +862,7 @@
     <t>table__Person.CountryRegion.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.CountryRegion.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.CountryRegion.sql</t>
   </si>
   <si>
     <t>5BB96BCDDBBDEBADF135B661C19B350B</t>
@@ -874,7 +874,7 @@
     <t>table__Person.EmailAddress.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.EmailAddress.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.EmailAddress.sql</t>
   </si>
   <si>
     <t>4B896C74F29899543C11EC768F32409B</t>
@@ -886,7 +886,7 @@
     <t>table__Person.Password.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.Password.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.Password.sql</t>
   </si>
   <si>
     <t>2E2A0FE95B210391BE42F9071EDE48BE</t>
@@ -898,7 +898,7 @@
     <t>table__Person.Person.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.Person.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.Person.sql</t>
   </si>
   <si>
     <t>CEA71116F62DA77C29D73CA35A022768</t>
@@ -910,7 +910,7 @@
     <t>table__Person.PersonPhone.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.PersonPhone.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.PersonPhone.sql</t>
   </si>
   <si>
     <t>60F9C8F4F9550E33504D90B5A74C70CC</t>
@@ -922,7 +922,7 @@
     <t>table__Person.PhoneNumberType.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.PhoneNumberType.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.PhoneNumberType.sql</t>
   </si>
   <si>
     <t>DBA25BAC265188C8967469364B9CE7FA</t>
@@ -934,7 +934,7 @@
     <t>table__Person.StateProvince.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Person.StateProvince.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Person.StateProvince.sql</t>
   </si>
   <si>
     <t>57D5CF4EEBA86A111B55FEEB79FFEDEC</t>
@@ -946,7 +946,7 @@
     <t>table__Production.BillOfMaterials.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.BillOfMaterials.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.BillOfMaterials.sql</t>
   </si>
   <si>
     <t>B41188C3DFF17B6A689AC8102D2BC1A6</t>
@@ -958,7 +958,7 @@
     <t>table__Production.Culture.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Culture.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.Culture.sql</t>
   </si>
   <si>
     <t>1C130C6BDF76C57176E59BF82D6F45E3</t>
@@ -970,7 +970,7 @@
     <t>table__Production.Document.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Document.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.Document.sql</t>
   </si>
   <si>
     <t>87223ADE7453748D59A4D77AB9161990</t>
@@ -982,7 +982,7 @@
     <t>table__Production.Illustration.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Illustration.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.Illustration.sql</t>
   </si>
   <si>
     <t>CDF25A85A06B21D4F894436430687C5F</t>
@@ -994,7 +994,7 @@
     <t>table__Production.Location.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Location.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.Location.sql</t>
   </si>
   <si>
     <t>0545BD908EB198803B1693015A3CE02B</t>
@@ -1006,7 +1006,7 @@
     <t>table__Production.Product.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.Product.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.Product.sql</t>
   </si>
   <si>
     <t>E1A2837A7C58D9A163BF2F99F4BA918D</t>
@@ -1018,7 +1018,7 @@
     <t>table__Production.ProductCategory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductCategory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductCategory.sql</t>
   </si>
   <si>
     <t>3E35F2E89EEF417646F4CB4FBC17592A</t>
@@ -1030,7 +1030,7 @@
     <t>table__Production.ProductCostHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductCostHistory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductCostHistory.sql</t>
   </si>
   <si>
     <t>4261C77ACD861463971A72947ADEF0EB</t>
@@ -1042,7 +1042,7 @@
     <t>table__Production.ProductDescription.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductDescription.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductDescription.sql</t>
   </si>
   <si>
     <t>0A97183ACE800325530795C427B00F6A</t>
@@ -1054,7 +1054,7 @@
     <t>table__Production.ProductDocument.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductDocument.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductDocument.sql</t>
   </si>
   <si>
     <t>0398181199286BC96BFF033204F24025</t>
@@ -1066,7 +1066,7 @@
     <t>table__Production.ProductInventory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductInventory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductInventory.sql</t>
   </si>
   <si>
     <t>46D249B5A8EFF075AB470002B5C668B6</t>
@@ -1078,7 +1078,7 @@
     <t>table__Production.ProductListPriceHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductListPriceHistory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductListPriceHistory.sql</t>
   </si>
   <si>
     <t>23E2E2CA129E8DD01419C2370395097F</t>
@@ -1090,7 +1090,7 @@
     <t>table__Production.ProductModel.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductModel.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductModel.sql</t>
   </si>
   <si>
     <t>D05E0BF2770E989EF1DE2CA52468EDF5</t>
@@ -1102,7 +1102,7 @@
     <t>table__Production.ProductModelIllustration.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductModelIllustration.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductModelIllustration.sql</t>
   </si>
   <si>
     <t>BD221B96177793334973969A64B4BEBC</t>
@@ -1114,7 +1114,7 @@
     <t>table__Production.ProductModelProductDescriptionCulture.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductModelProductDescriptionCulture.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductModelProductDescriptionCulture.sql</t>
   </si>
   <si>
     <t>F35D2447ADCD0DA859EAF287626D974A</t>
@@ -1126,7 +1126,7 @@
     <t>table__Production.ProductPhoto.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductPhoto.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductPhoto.sql</t>
   </si>
   <si>
     <t>03C219754DA19CB82B6FD396EB6F28C5</t>
@@ -1138,7 +1138,7 @@
     <t>table__Production.ProductProductPhoto.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductProductPhoto.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductProductPhoto.sql</t>
   </si>
   <si>
     <t>876476D3B77644342259555E0A10E5F1</t>
@@ -1150,7 +1150,7 @@
     <t>table__Production.ProductReview.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductReview.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductReview.sql</t>
   </si>
   <si>
     <t>7C377BBF6513688CA880F9F9D0F1D76E</t>
@@ -1162,7 +1162,7 @@
     <t>table__Production.ProductSubcategory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ProductSubcategory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ProductSubcategory.sql</t>
   </si>
   <si>
     <t>EA8F0B633FC9352809AB4AB26BDA306C</t>
@@ -1174,7 +1174,7 @@
     <t>table__Production.ScrapReason.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.ScrapReason.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.ScrapReason.sql</t>
   </si>
   <si>
     <t>C2AD160F44D5EDD63F11596C05CCBA51</t>
@@ -1186,7 +1186,7 @@
     <t>table__Production.TransactionHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.TransactionHistory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.TransactionHistory.sql</t>
   </si>
   <si>
     <t>13719707E5535F85CF798C7F5DAF155B</t>
@@ -1198,7 +1198,7 @@
     <t>table__Production.TransactionHistoryArchive.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.TransactionHistoryArchive.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.TransactionHistoryArchive.sql</t>
   </si>
   <si>
     <t>544F70FCAE619680F6C9951951608CDD</t>
@@ -1210,7 +1210,7 @@
     <t>table__Production.UnitMeasure.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.UnitMeasure.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.UnitMeasure.sql</t>
   </si>
   <si>
     <t>E24E10E408A06B9F5C59D83FF0CA225D</t>
@@ -1222,7 +1222,7 @@
     <t>table__Production.WorkOrder.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.WorkOrder.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.WorkOrder.sql</t>
   </si>
   <si>
     <t>41344D16748C45BF0868FF364D49878E</t>
@@ -1234,7 +1234,7 @@
     <t>table__Production.WorkOrderRouting.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Production.WorkOrderRouting.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Production.WorkOrderRouting.sql</t>
   </si>
   <si>
     <t>B08836F89C3812FCAD7848493AC6C222</t>
@@ -1246,7 +1246,7 @@
     <t>table__Purchasing.ProductVendor.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.ProductVendor.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Purchasing.ProductVendor.sql</t>
   </si>
   <si>
     <t>9E2E628A6B381784205541577DB178F3</t>
@@ -1258,7 +1258,7 @@
     <t>table__Purchasing.PurchaseOrderDetail.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderDetail.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderDetail.sql</t>
   </si>
   <si>
     <t>36588C425A912EBB636171FA624E54CA</t>
@@ -1270,7 +1270,7 @@
     <t>table__Purchasing.PurchaseOrderHeader.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderHeader.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Purchasing.PurchaseOrderHeader.sql</t>
   </si>
   <si>
     <t>B5FF0036905B4D6641D97D3DD82A9125</t>
@@ -1282,7 +1282,7 @@
     <t>table__Purchasing.ShipMethod.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.ShipMethod.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Purchasing.ShipMethod.sql</t>
   </si>
   <si>
     <t>53C0287AFAFB7FACD5130ABA4F5A63DC</t>
@@ -1294,7 +1294,7 @@
     <t>table__Purchasing.Vendor.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Purchasing.Vendor.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Purchasing.Vendor.sql</t>
   </si>
   <si>
     <t>0C3481C46FCF8839B53FA1C7AF77D661</t>
@@ -1306,7 +1306,7 @@
     <t>table__Sales.CountryRegionCurrency.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.CountryRegionCurrency.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.CountryRegionCurrency.sql</t>
   </si>
   <si>
     <t>CB23C961AD6C0967CBCE83F7B7D4252F</t>
@@ -1318,7 +1318,7 @@
     <t>table__Sales.CreditCard.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.CreditCard.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.CreditCard.sql</t>
   </si>
   <si>
     <t>86C19DBC9CB4B9BE848969BB70852DB6</t>
@@ -1330,7 +1330,7 @@
     <t>table__Sales.Currency.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.Currency.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.Currency.sql</t>
   </si>
   <si>
     <t>49DA4C335C4301DABE0D4AC5791CA07F</t>
@@ -1342,7 +1342,7 @@
     <t>table__Sales.CurrencyRate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.CurrencyRate.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.CurrencyRate.sql</t>
   </si>
   <si>
     <t>A58B28FFBB12FBB0CA0E3766DF35B07E</t>
@@ -1354,7 +1354,7 @@
     <t>table__Sales.Customer.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.Customer.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.Customer.sql</t>
   </si>
   <si>
     <t>E6FC49B6E1B25B07E04DF33CE45F4399</t>
@@ -1366,7 +1366,7 @@
     <t>table__Sales.PersonCreditCard.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.PersonCreditCard.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.PersonCreditCard.sql</t>
   </si>
   <si>
     <t>A241FDEF93235427CF91A5507973980F</t>
@@ -1378,7 +1378,7 @@
     <t>table__Sales.SalesOrderDetail.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesOrderDetail.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SalesOrderDetail.sql</t>
   </si>
   <si>
     <t>E1099694C073E244D0B1732BFE40C2AB</t>
@@ -1390,7 +1390,7 @@
     <t>table__Sales.SalesOrderHeader.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeader.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeader.sql</t>
   </si>
   <si>
     <t>7354A80681291374434F107181B3B86A</t>
@@ -1402,7 +1402,7 @@
     <t>table__Sales.SalesOrderHeaderSalesReason.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeaderSalesReason.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SalesOrderHeaderSalesReason.sql</t>
   </si>
   <si>
     <t>7A24418F81E279698B5FF138D4BFB170</t>
@@ -1414,7 +1414,7 @@
     <t>table__Sales.SalesPerson.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesPerson.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SalesPerson.sql</t>
   </si>
   <si>
     <t>49179896BB64CA95587BABDD2A7E43D4</t>
@@ -1426,7 +1426,7 @@
     <t>table__Sales.SalesPersonQuotaHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesPersonQuotaHistory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SalesPersonQuotaHistory.sql</t>
   </si>
   <si>
     <t>FDEE90B15CAD405E463BFF80FD75EF34</t>
@@ -1438,7 +1438,7 @@
     <t>table__Sales.SalesReason.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesReason.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SalesReason.sql</t>
   </si>
   <si>
     <t>47485D008572AEEFECB84EE3E0F1DE6E</t>
@@ -1450,7 +1450,7 @@
     <t>table__Sales.SalesTaxRate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesTaxRate.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SalesTaxRate.sql</t>
   </si>
   <si>
     <t>32719803958AC6D18D90AA966A22B082</t>
@@ -1462,7 +1462,7 @@
     <t>table__Sales.SalesTerritory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesTerritory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SalesTerritory.sql</t>
   </si>
   <si>
     <t>B790E7EFC56E9AC828FFDE5038CFADB6</t>
@@ -1474,7 +1474,7 @@
     <t>table__Sales.SalesTerritoryHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SalesTerritoryHistory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SalesTerritoryHistory.sql</t>
   </si>
   <si>
     <t>1244394A085CB4B94173FDD051942941</t>
@@ -1486,7 +1486,7 @@
     <t>table__Sales.ShoppingCartItem.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.ShoppingCartItem.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.ShoppingCartItem.sql</t>
   </si>
   <si>
     <t>9EE4E094750CB2905440942505351ADA</t>
@@ -1498,7 +1498,7 @@
     <t>table__Sales.SpecialOffer.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SpecialOffer.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SpecialOffer.sql</t>
   </si>
   <si>
     <t>F34B35578D75C869E165D90095D3E093</t>
@@ -1510,7 +1510,7 @@
     <t>table__Sales.SpecialOfferProduct.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.SpecialOfferProduct.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.SpecialOfferProduct.sql</t>
   </si>
   <si>
     <t>90353DD5FEA1EE6BC0D43B195EE9727F</t>
@@ -1522,7 +1522,7 @@
     <t>table__Sales.Store.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__Sales.Store.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__Sales.Store.sql</t>
   </si>
   <si>
     <t>73C4AAD5EC0DEF9534BCA7A958692CEC</t>
@@ -1534,7 +1534,7 @@
     <t>table__dbo.AWBuildVersion.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__dbo.AWBuildVersion.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__dbo.AWBuildVersion.sql</t>
   </si>
   <si>
     <t>Incorrect Analysis Warning: 1, Total Statement count: 1, Conventional Statement count: 1, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 0, High category breaks: 0</t>
@@ -1549,7 +1549,7 @@
     <t>table__dbo.DatabaseLog.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__dbo.DatabaseLog.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__dbo.DatabaseLog.sql</t>
   </si>
   <si>
     <t>F0343BA0E4E0A37B096257477CFF2588</t>
@@ -1561,7 +1561,7 @@
     <t>table__dbo.ErrorLog.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/table__dbo.ErrorLog.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/table__dbo.ErrorLog.sql</t>
   </si>
   <si>
     <t>4163DE2662EE1C6C040E46334FE032D2</t>
@@ -1573,7 +1573,7 @@
     <t>view__HumanResources.vEmployee.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vEmployee.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__HumanResources.vEmployee.sql</t>
   </si>
   <si>
     <t>CREATE_VIEW</t>
@@ -1588,7 +1588,7 @@
     <t>view__HumanResources.vEmployeeDepartment.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartment.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartment.sql</t>
   </si>
   <si>
     <t>679B2E1E4FFFF228E3C17A5AF6EAB185</t>
@@ -1600,7 +1600,7 @@
     <t>view__HumanResources.vEmployeeDepartmentHistory.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartmentHistory.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__HumanResources.vEmployeeDepartmentHistory.sql</t>
   </si>
   <si>
     <t>50C7657DBE2E158414B1BEE40DE7858D</t>
@@ -1612,7 +1612,7 @@
     <t>view__HumanResources.vJobCandidate.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidate.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidate.sql</t>
   </si>
   <si>
     <t>CREATE_VIEW,UNKNOWN,VAR_DECLARE</t>
@@ -1630,7 +1630,7 @@
     <t>view__HumanResources.vJobCandidateEducation.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEducation.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEducation.sql</t>
   </si>
   <si>
     <t>Incorrect Analysis Warning: 1, Total Statement count: 14, Conventional Statement count: 14, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1645,7 +1645,7 @@
     <t>view__HumanResources.vJobCandidateEmployment.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEmployment.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__HumanResources.vJobCandidateEmployment.sql</t>
   </si>
   <si>
     <t>Incorrect Analysis Warning: 1, Total Statement count: 12, Conventional Statement count: 12, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1660,7 +1660,7 @@
     <t>view__Person.vAdditionalContactInfo.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Person.vAdditionalContactInfo.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Person.vAdditionalContactInfo.sql</t>
   </si>
   <si>
     <t>Total Statement count: 24, Conventional Statement count: 13, Simple Statement count: 11, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1675,7 +1675,7 @@
     <t>view__Person.vStateProvinceCountryRegion.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Person.vStateProvinceCountryRegion.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Person.vStateProvinceCountryRegion.sql</t>
   </si>
   <si>
     <t>D1B666575C3150FA07161F6E1A8129F0</t>
@@ -1687,7 +1687,7 @@
     <t>view__Production.vProductAndDescription.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Production.vProductAndDescription.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Production.vProductAndDescription.sql</t>
   </si>
   <si>
     <t>AD0C95888E8820742BAA5DE17B3A96AA</t>
@@ -1699,7 +1699,7 @@
     <t>view__Production.vProductModelCatalogDescription.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Production.vProductModelCatalogDescription.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Production.vProductModelCatalogDescription.sql</t>
   </si>
   <si>
     <t>Total Statement count: 32, Conventional Statement count: 22, Simple Statement count: 10, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1714,7 +1714,7 @@
     <t>view__Production.vProductModelInstructions.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Production.vProductModelInstructions.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Production.vProductModelInstructions.sql</t>
   </si>
   <si>
     <t>1A47F8B4BC2B7ACEDB60EE1B1AAD4470</t>
@@ -1726,7 +1726,7 @@
     <t>view__Purchasing.vVendorWithAddresses.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithAddresses.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithAddresses.sql</t>
   </si>
   <si>
     <t>D7CD68F5F89F8956B1DBD51AB75496CB</t>
@@ -1738,7 +1738,7 @@
     <t>view__Purchasing.vVendorWithContacts.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithContacts.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Purchasing.vVendorWithContacts.sql</t>
   </si>
   <si>
     <t>8FCD0C6976595D45BF4770D9FAA0EC11</t>
@@ -1750,7 +1750,7 @@
     <t>view__Sales.vIndividualCustomer.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vIndividualCustomer.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Sales.vIndividualCustomer.sql</t>
   </si>
   <si>
     <t>AA4431CE6421DCB43574B5BCCB8273B5</t>
@@ -1762,7 +1762,7 @@
     <t>view__Sales.vPersonDemographics.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vPersonDemographics.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Sales.vPersonDemographics.sql</t>
   </si>
   <si>
     <t>Total Statement count: 14, Conventional Statement count: 14, Simple Statement count: 0, Pivot functions: 0, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1777,7 +1777,7 @@
     <t>view__Sales.vSalesPerson.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vSalesPerson.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Sales.vSalesPerson.sql</t>
   </si>
   <si>
     <t>090AE69AE0362DEA70853EFBAE038CE7</t>
@@ -1789,7 +1789,7 @@
     <t>view__Sales.vSalesPersonSalesByFiscalYears.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vSalesPersonSalesByFiscalYears.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Sales.vSalesPersonSalesByFiscalYears.sql</t>
   </si>
   <si>
     <t>Total Statement count: 1, Conventional Statement count: 1, Simple Statement count: 0, Pivot functions: 1, XML functions: 0, Loops: 0, Medium category breaks: 1, High category breaks: 0</t>
@@ -1804,7 +1804,7 @@
     <t>view__Sales.vStoreWithAddresses.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vStoreWithAddresses.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Sales.vStoreWithAddresses.sql</t>
   </si>
   <si>
     <t>0AFF094C65B3C3F48B8130C48F8F6294</t>
@@ -1816,7 +1816,7 @@
     <t>view__Sales.vStoreWithContacts.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vStoreWithContacts.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Sales.vStoreWithContacts.sql</t>
   </si>
   <si>
     <t>C707BD34FAA1443727F92838D30983B9</t>
@@ -1828,7 +1828,7 @@
     <t>view__Sales.vStoreWithDemographics.sql</t>
   </si>
   <si>
-    <t>/home/milind-joshi/mig_dbx/migration_codes/output_lakebridge/_source_export/sql/view__Sales.vStoreWithDemographics.sql</t>
+    <t>D:/autovista_clean/output_lakebridge/_source_export/sql/view__Sales.vStoreWithDemographics.sql</t>
   </si>
   <si>
     <t>06140F8E409F58532DAB1C311FA4E9B9</t>
@@ -2047,82 +2047,82 @@
     <t>ISNULL</t>
   </si>
   <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>COALESCE</t>
+  </si>
+  <si>
     <t>OPTION</t>
   </si>
   <si>
-    <t>COALESCE</t>
-  </si>
-  <si>
-    <t>TEXT</t>
-  </si>
-  <si>
     <t>ERROR_NUMBER</t>
   </si>
   <si>
     <t>CONTAINSTABLE</t>
   </si>
   <si>
+    <t>SQL:COLUMN</t>
+  </si>
+  <si>
+    <t>ERROR_MESSAGE</t>
+  </si>
+  <si>
+    <t>ERROR_LINE</t>
+  </si>
+  <si>
+    <t>RAISERROR</t>
+  </si>
+  <si>
     <t>DATEADD</t>
   </si>
   <si>
-    <t>RAISERROR</t>
+    <t>ERROR_SEVERITY</t>
+  </si>
+  <si>
+    <t>ERROR_PROCEDURE</t>
+  </si>
+  <si>
+    <t>OF</t>
   </si>
   <si>
     <t>ERROR_STATE</t>
   </si>
   <si>
-    <t>ERROR_PROCEDURE</t>
-  </si>
-  <si>
-    <t>OF</t>
-  </si>
-  <si>
-    <t>ERROR_MESSAGE</t>
-  </si>
-  <si>
-    <t>SQL:COLUMN</t>
-  </si>
-  <si>
-    <t>ERROR_SEVERITY</t>
-  </si>
-  <si>
-    <t>ERROR_LINE</t>
+    <t>XACT_STATE</t>
+  </si>
+  <si>
+    <t>FREETEXTTABLE</t>
+  </si>
+  <si>
+    <t>YEAR</t>
+  </si>
+  <si>
+    <t>COUNT</t>
+  </si>
+  <si>
+    <t>INTO</t>
+  </si>
+  <si>
+    <t>NUMERIC</t>
+  </si>
+  <si>
+    <t>SERVERPROPERTY</t>
+  </si>
+  <si>
+    <t>DATALENGTH</t>
   </si>
   <si>
     <t>PIVOT</t>
   </si>
   <si>
-    <t>XACT_STATE</t>
-  </si>
-  <si>
     <t>REPLICATE</t>
   </si>
   <si>
-    <t>SERVERPROPERTY</t>
-  </si>
-  <si>
-    <t>DATALENGTH</t>
-  </si>
-  <si>
-    <t>COUNT</t>
-  </si>
-  <si>
-    <t>FREETEXTTABLE</t>
-  </si>
-  <si>
-    <t>YEAR</t>
+    <t>REPLACE</t>
   </si>
   <si>
     <t>STRING</t>
-  </si>
-  <si>
-    <t>INTO</t>
-  </si>
-  <si>
-    <t>REPLACE</t>
-  </si>
-  <si>
-    <t>NUMERIC</t>
   </si>
   <si>
     <t>Script</t>
@@ -3576,7 +3576,7 @@
         <v>673</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>704</v>
@@ -5353,7 +5353,7 @@
         <v>153</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>698</v>
@@ -9154,7 +9154,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="6" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="B21" s="6">
         <v>1</v>
@@ -14864,54 +14864,54 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>540</v>
+        <v>362</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C2" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>540</v>
+        <v>322</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C3" s="6">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>414</v>
+        <v>322</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C4" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>553</v>
+        <v>358</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C5" s="6">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>212</v>
+        <v>76</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -14919,21 +14919,21 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>212</v>
+        <v>76</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>680</v>
+        <v>665</v>
       </c>
       <c r="C7" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>212</v>
+        <v>342</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
@@ -14941,21 +14941,21 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>212</v>
+        <v>122</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>615</v>
+        <v>671</v>
       </c>
       <c r="C9" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
-        <v>212</v>
+        <v>122</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="C10" s="6">
         <v>2</v>
@@ -14963,10 +14963,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -14974,21 +14974,21 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
-        <v>286</v>
+        <v>100</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C12" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
-        <v>470</v>
+        <v>100</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>663</v>
+        <v>690</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -14996,10 +14996,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
-        <v>294</v>
+        <v>100</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>663</v>
+        <v>692</v>
       </c>
       <c r="C14" s="6">
         <v>1</v>
@@ -15007,10 +15007,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
-        <v>334</v>
+        <v>136</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -15018,32 +15018,32 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>290</v>
+        <v>136</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="C16" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
-        <v>486</v>
+        <v>136</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C17" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
-        <v>583</v>
+        <v>290</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>683</v>
+        <v>663</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
@@ -15051,21 +15051,21 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
-        <v>583</v>
+        <v>224</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>690</v>
+        <v>663</v>
       </c>
       <c r="C19" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>583</v>
+        <v>278</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
@@ -15073,10 +15073,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
-        <v>583</v>
+        <v>177</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="C21" s="6">
         <v>1</v>
@@ -15084,43 +15084,43 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="6" t="s">
-        <v>583</v>
+        <v>535</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C22" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>663</v>
+        <v>693</v>
       </c>
       <c r="C23" s="6">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>183</v>
+        <v>535</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>615</v>
+        <v>665</v>
       </c>
       <c r="C24" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>183</v>
+        <v>326</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C25" s="6">
         <v>1</v>
@@ -15128,21 +15128,21 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C26" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>326</v>
+        <v>153</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>663</v>
+        <v>689</v>
       </c>
       <c r="C27" s="6">
         <v>1</v>
@@ -15150,10 +15150,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C28" s="6">
         <v>1</v>
@@ -15161,10 +15161,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="C29" s="6">
         <v>1</v>
@@ -15175,51 +15175,51 @@
         <v>153</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C30" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="6" t="s">
-        <v>153</v>
+        <v>434</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C31" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="6" t="s">
-        <v>153</v>
+        <v>418</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>686</v>
+        <v>663</v>
       </c>
       <c r="C32" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>153</v>
+        <v>212</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>689</v>
+        <v>615</v>
       </c>
       <c r="C33" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
-        <v>153</v>
+        <v>212</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C34" s="6">
         <v>1</v>
@@ -15227,32 +15227,32 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="C35" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>128</v>
+        <v>212</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="C36" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>278</v>
+        <v>212</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C37" s="6">
         <v>1</v>
@@ -15260,21 +15260,21 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="6" t="s">
-        <v>218</v>
+        <v>450</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="C38" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C39" s="6">
         <v>2</v>
@@ -15282,43 +15282,43 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
-        <v>386</v>
+        <v>230</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C40" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>362</v>
+        <v>494</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C41" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="6" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C42" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="6" t="s">
-        <v>76</v>
+        <v>382</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C43" s="6">
         <v>1</v>
@@ -15326,65 +15326,65 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="6" t="s">
-        <v>76</v>
+        <v>474</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C44" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="6" t="s">
-        <v>132</v>
+        <v>530</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C45" s="6">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="6" t="s">
-        <v>426</v>
+        <v>498</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C46" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="6" t="s">
-        <v>140</v>
+        <v>218</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C47" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="6" t="s">
-        <v>140</v>
+        <v>218</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>679</v>
+        <v>615</v>
       </c>
       <c r="C48" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="6" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="C49" s="6">
         <v>1</v>
@@ -15392,10 +15392,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="6" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -15403,21 +15403,21 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="6" t="s">
-        <v>140</v>
+        <v>286</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="C51" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="6" t="s">
-        <v>140</v>
+        <v>286</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="C52" s="6">
         <v>1</v>
@@ -15425,32 +15425,32 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="6" t="s">
-        <v>140</v>
+        <v>524</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="C53" s="6">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="6" t="s">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>684</v>
+        <v>663</v>
       </c>
       <c r="C54" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="6" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>685</v>
+        <v>670</v>
       </c>
       <c r="C55" s="6">
         <v>1</v>
@@ -15458,7 +15458,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="6" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>665</v>
@@ -15469,21 +15469,21 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="6" t="s">
-        <v>100</v>
+        <v>503</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="C57" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="6" t="s">
-        <v>254</v>
+        <v>446</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="C58" s="6">
         <v>1</v>
@@ -15491,10 +15491,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="6" t="s">
-        <v>51</v>
+        <v>446</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C59" s="6">
         <v>1</v>
@@ -15502,10 +15502,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="6" t="s">
-        <v>51</v>
+        <v>414</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="C60" s="6">
         <v>1</v>
@@ -15513,21 +15513,21 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="6" t="s">
-        <v>382</v>
+        <v>507</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C61" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="6" t="s">
-        <v>136</v>
+        <v>378</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -15535,21 +15535,21 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="6" t="s">
-        <v>136</v>
+        <v>302</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C63" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="6" t="s">
-        <v>136</v>
+        <v>350</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C64" s="6">
         <v>1</v>
@@ -15557,18 +15557,18 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="6" t="s">
-        <v>503</v>
+        <v>254</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C65" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="6" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>663</v>
@@ -15579,21 +15579,21 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="6" t="s">
-        <v>274</v>
+        <v>430</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C67" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="6" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -15601,87 +15601,87 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="6" t="s">
-        <v>270</v>
+        <v>553</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C69" s="6">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="6" t="s">
-        <v>370</v>
+        <v>558</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>663</v>
+        <v>694</v>
       </c>
       <c r="C70" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="6" t="s">
-        <v>250</v>
+        <v>558</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C71" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="6" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C72" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="6" t="s">
-        <v>201</v>
+        <v>596</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="C73" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="6" t="s">
-        <v>201</v>
+        <v>298</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C74" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="6" t="s">
-        <v>201</v>
+        <v>298</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C75" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="6" t="s">
-        <v>498</v>
+        <v>140</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C76" s="6">
         <v>1</v>
@@ -15689,21 +15689,21 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="6" t="s">
-        <v>306</v>
+        <v>140</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="C77" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="6" t="s">
-        <v>306</v>
+        <v>140</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="C78" s="6">
         <v>1</v>
@@ -15711,10 +15711,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="6" t="s">
-        <v>302</v>
+        <v>140</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="C79" s="6">
         <v>1</v>
@@ -15722,10 +15722,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="6" t="s">
-        <v>390</v>
+        <v>140</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="C80" s="6">
         <v>1</v>
@@ -15733,10 +15733,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="6" t="s">
-        <v>390</v>
+        <v>140</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>664</v>
+        <v>683</v>
       </c>
       <c r="C81" s="6">
         <v>1</v>
@@ -15744,10 +15744,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="6" t="s">
-        <v>494</v>
+        <v>140</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>663</v>
+        <v>676</v>
       </c>
       <c r="C82" s="6">
         <v>1</v>
@@ -15755,21 +15755,21 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="6" t="s">
-        <v>535</v>
+        <v>140</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>663</v>
+        <v>682</v>
       </c>
       <c r="C83" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="6" t="s">
-        <v>535</v>
+        <v>189</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="C84" s="6">
         <v>1</v>
@@ -15777,10 +15777,10 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="6" t="s">
-        <v>535</v>
+        <v>189</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="C85" s="6">
         <v>1</v>
@@ -15788,21 +15788,21 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="6" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>615</v>
+        <v>677</v>
       </c>
       <c r="C86" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="6" t="s">
-        <v>171</v>
+        <v>310</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>692</v>
+        <v>664</v>
       </c>
       <c r="C87" s="6">
         <v>1</v>
@@ -15810,51 +15810,51 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="6" t="s">
-        <v>374</v>
+        <v>310</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C88" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="6" t="s">
-        <v>224</v>
+        <v>318</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C89" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="6" t="s">
-        <v>230</v>
+        <v>390</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C90" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="6" t="s">
-        <v>230</v>
+        <v>390</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C91" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="6" t="s">
-        <v>310</v>
+        <v>386</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>664</v>
@@ -15865,54 +15865,54 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="6" t="s">
-        <v>310</v>
+        <v>374</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C93" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="6" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C94" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="6" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>615</v>
       </c>
       <c r="C95" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="6" t="s">
-        <v>450</v>
+        <v>183</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C96" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="6" t="s">
-        <v>482</v>
+        <v>51</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C97" s="6">
         <v>1</v>
@@ -15920,10 +15920,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="6" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="C98" s="6">
         <v>1</v>
@@ -15931,10 +15931,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="6" t="s">
-        <v>70</v>
+        <v>246</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C99" s="6">
         <v>1</v>
@@ -15942,21 +15942,21 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="6" t="s">
-        <v>507</v>
+        <v>274</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>663</v>
       </c>
       <c r="C100" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="6" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="C101" s="6">
         <v>1</v>
@@ -15964,10 +15964,10 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="6" t="s">
-        <v>147</v>
+        <v>270</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="C102" s="6">
         <v>1</v>
@@ -15975,21 +15975,21 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="6" t="s">
-        <v>147</v>
+        <v>486</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C103" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="6" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>672</v>
+        <v>615</v>
       </c>
       <c r="C104" s="6">
         <v>1</v>
@@ -15997,21 +15997,21 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="6" t="s">
-        <v>147</v>
+        <v>466</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>682</v>
+        <v>663</v>
       </c>
       <c r="C105" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="6" t="s">
-        <v>147</v>
+        <v>470</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="C106" s="6">
         <v>1</v>
@@ -16019,21 +16019,21 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="6" t="s">
-        <v>147</v>
+        <v>306</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C107" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="6" t="s">
-        <v>147</v>
+        <v>306</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="C108" s="6">
         <v>1</v>
@@ -16041,21 +16041,21 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="6" t="s">
-        <v>422</v>
+        <v>171</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>663</v>
+        <v>615</v>
       </c>
       <c r="C109" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="6" t="s">
-        <v>422</v>
+        <v>171</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
       <c r="C110" s="6">
         <v>1</v>
@@ -16063,54 +16063,54 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="6" t="s">
-        <v>430</v>
+        <v>201</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>664</v>
+        <v>615</v>
       </c>
       <c r="C111" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="6" t="s">
-        <v>430</v>
+        <v>201</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="6" t="s">
-        <v>466</v>
+        <v>201</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C113" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="6" t="s">
-        <v>298</v>
+        <v>583</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>663</v>
+        <v>685</v>
       </c>
       <c r="C114" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="6" t="s">
-        <v>298</v>
+        <v>583</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="C115" s="6">
         <v>1</v>
@@ -16118,18 +16118,18 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="6" t="s">
-        <v>524</v>
+        <v>583</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="C116" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="6" t="s">
-        <v>558</v>
+        <v>583</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>691</v>
@@ -16140,10 +16140,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="6" t="s">
-        <v>558</v>
+        <v>583</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C118" s="6">
         <v>1</v>
@@ -16151,21 +16151,21 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="6" t="s">
-        <v>558</v>
+        <v>60</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C119" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="6" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="C120" s="6">
         <v>1</v>
@@ -16173,10 +16173,10 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="6" t="s">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C121" s="6">
         <v>1</v>
@@ -16184,10 +16184,10 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="6" t="s">
-        <v>350</v>
+        <v>132</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C122" s="6">
         <v>1</v>
@@ -16195,40 +16195,40 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="6" t="s">
-        <v>434</v>
+        <v>540</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="C123" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="6" t="s">
-        <v>94</v>
+        <v>540</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="6" t="s">
-        <v>446</v>
+        <v>370</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>694</v>
+        <v>663</v>
       </c>
       <c r="C125" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="6" t="s">
-        <v>446</v>
+        <v>334</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>663</v>
@@ -16239,10 +16239,10 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="6" t="s">
-        <v>378</v>
+        <v>195</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C127" s="6">
         <v>1</v>
@@ -16250,32 +16250,32 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="6" t="s">
-        <v>322</v>
+        <v>195</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C128" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="6" t="s">
-        <v>322</v>
+        <v>94</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C129" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="6" t="s">
-        <v>122</v>
+        <v>402</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="C130" s="6">
         <v>1</v>
@@ -16283,21 +16283,21 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="6" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>668</v>
       </c>
       <c r="C131" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="6" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -16305,21 +16305,21 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="6" t="s">
-        <v>474</v>
+        <v>147</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="C133" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="6" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -16327,10 +16327,10 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="6" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C135" s="6">
         <v>1</v>
@@ -16338,10 +16338,10 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="6" t="s">
-        <v>358</v>
+        <v>147</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -16349,21 +16349,21 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="6" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>665</v>
       </c>
       <c r="C137" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="6" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -16371,10 +16371,10 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="6" t="s">
-        <v>177</v>
+        <v>482</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C139" s="6">
         <v>1</v>
@@ -16500,83 +16500,89 @@
     </row>
     <row r="2" spans="1:34">
       <c r="A2" s="6" t="s">
-        <v>540</v>
+        <v>362</v>
       </c>
       <c r="B2" s="6">
-        <v>11</v>
-      </c>
-      <c r="K2" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:34">
       <c r="A3" s="6" t="s">
-        <v>414</v>
+        <v>322</v>
       </c>
       <c r="B3" s="6">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C3" s="6">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:34">
       <c r="A4" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="B4" s="6">
-        <v>21</v>
+        <v>358</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:34">
       <c r="A5" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" s="6">
-        <v>4</v>
-      </c>
-      <c r="F5" s="6">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6">
-        <v>1</v>
-      </c>
-      <c r="R5" s="6">
-        <v>2</v>
-      </c>
-      <c r="T5" s="6">
-        <v>2</v>
+        <v>76</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:34">
       <c r="A6" s="6" t="s">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="B6" s="6">
-        <v>5</v>
-      </c>
-      <c r="C6" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:34">
       <c r="A7" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="B7" s="6">
+        <v>122</v>
+      </c>
+      <c r="F7" s="6">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6">
+        <v>2</v>
+      </c>
+      <c r="K7" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:34">
       <c r="A8" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="B8" s="6">
+        <v>100</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:34">
       <c r="A9" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="B9" s="6">
+        <v>136</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6">
+        <v>2</v>
+      </c>
+      <c r="K9" s="6">
         <v>1</v>
       </c>
     </row>
@@ -16590,54 +16596,45 @@
     </row>
     <row r="11" spans="1:34">
       <c r="A11" s="6" t="s">
-        <v>486</v>
+        <v>224</v>
       </c>
       <c r="B11" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:34">
       <c r="A12" s="6" t="s">
-        <v>583</v>
-      </c>
-      <c r="F12" s="6">
-        <v>1</v>
-      </c>
-      <c r="J12" s="6">
-        <v>1</v>
-      </c>
-      <c r="N12" s="6">
-        <v>1</v>
-      </c>
-      <c r="W12" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="6">
+        <v>278</v>
+      </c>
+      <c r="B12" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:34">
       <c r="A13" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="B13" s="6">
-        <v>12</v>
+        <v>177</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:34">
       <c r="A14" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D14" s="6">
-        <v>2</v>
-      </c>
-      <c r="G14" s="6">
+        <v>535</v>
+      </c>
+      <c r="B14" s="6">
+        <v>10</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:34">
       <c r="A15" s="6" t="s">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="B15" s="6">
         <v>1</v>
@@ -16645,670 +16642,673 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16" s="6" t="s">
-        <v>326</v>
+        <v>153</v>
       </c>
       <c r="B16" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:29">
+      <c r="E16" s="6">
+        <v>1</v>
+      </c>
+      <c r="M16" s="6">
+        <v>3</v>
+      </c>
+      <c r="X16" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F17" s="6">
-        <v>1</v>
-      </c>
-      <c r="G17" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29">
+        <v>434</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="6" t="s">
-        <v>153</v>
+        <v>418</v>
       </c>
       <c r="B18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1</v>
-      </c>
-      <c r="M18" s="6">
         <v>3</v>
       </c>
-      <c r="Z18" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D19" s="6">
+        <v>4</v>
+      </c>
+      <c r="F19" s="6">
+        <v>1</v>
+      </c>
+      <c r="G19" s="6">
+        <v>1</v>
+      </c>
+      <c r="N19" s="6">
+        <v>2</v>
+      </c>
+      <c r="U19" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="B20" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" s="6">
+        <v>3</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="B22" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="B23" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B25" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="B26" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="B27" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D28" s="6">
+        <v>2</v>
+      </c>
+      <c r="F28" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B29" s="6">
+        <v>1</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B30" s="6">
+        <v>5</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B31" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B32" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34">
+      <c r="A33" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1</v>
+      </c>
+      <c r="J33" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34">
+      <c r="A34" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="B34" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34">
+      <c r="A35" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B35" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34">
+      <c r="A36" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="B36" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34">
+      <c r="A37" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B37" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:34">
+      <c r="A38" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B38" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:34">
+      <c r="A39" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C39" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:34">
+      <c r="A40" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B40" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:34">
+      <c r="A41" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B41" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:34">
+      <c r="A42" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B42" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:34">
+      <c r="A43" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B43" s="6">
+        <v>1</v>
+      </c>
+      <c r="C43" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:34">
+      <c r="A44" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="B44" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:34">
+      <c r="A45" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="B45" s="6">
+        <v>2</v>
+      </c>
+      <c r="I45" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH45" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:34">
+      <c r="A46" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="B46" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:34">
+      <c r="A47" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B47" s="6">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:34">
+      <c r="A48" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E48" s="6">
+        <v>1</v>
+      </c>
+      <c r="L48" s="6">
+        <v>2</v>
+      </c>
+      <c r="O48" s="6">
+        <v>1</v>
+      </c>
+      <c r="P48" s="6">
+        <v>1</v>
+      </c>
+      <c r="S48" s="6">
+        <v>1</v>
+      </c>
+      <c r="T48" s="6">
+        <v>1</v>
+      </c>
+      <c r="V48" s="6">
+        <v>1</v>
+      </c>
+      <c r="W48" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26">
+      <c r="A49" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26">
+      <c r="A50" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="O19" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29">
-      <c r="A20" s="6" t="s">
+      <c r="Q50" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26">
+      <c r="A51" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B51" s="6">
+        <v>4</v>
+      </c>
+      <c r="C51" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26">
+      <c r="A52" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B52" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26">
+      <c r="A53" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B53" s="6">
+        <v>1</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26">
+      <c r="A54" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26">
+      <c r="A55" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B55" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26">
+      <c r="A56" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B56" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26">
+      <c r="A57" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D57" s="6">
+        <v>2</v>
+      </c>
+      <c r="G57" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26">
+      <c r="A58" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1</v>
+      </c>
+      <c r="R58" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26">
+      <c r="A59" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B59" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26">
+      <c r="A60" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B60" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26">
+      <c r="A61" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I20" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29">
-      <c r="A21" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B21" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29">
-      <c r="A22" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2</v>
-      </c>
-      <c r="F22" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29">
-      <c r="A23" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29">
-      <c r="A24" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="B24" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
-      <c r="A25" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="B25" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29">
-      <c r="A26" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1</v>
-      </c>
-      <c r="J26" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29">
-      <c r="A27" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="I27" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29">
-      <c r="A28" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="B28" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29">
-      <c r="A29" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29" s="6">
-        <v>1</v>
-      </c>
-      <c r="L29" s="6">
-        <v>2</v>
-      </c>
-      <c r="P29" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>1</v>
-      </c>
-      <c r="S29" s="6">
-        <v>1</v>
-      </c>
-      <c r="U29" s="6">
-        <v>1</v>
-      </c>
-      <c r="V29" s="6">
-        <v>1</v>
-      </c>
-      <c r="X29" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29">
-      <c r="A30" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E30" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA30" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29">
-      <c r="A31" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B31" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29">
-      <c r="A32" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="6">
-        <v>1</v>
-      </c>
-      <c r="N32" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="C33" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F34" s="6">
-        <v>1</v>
-      </c>
-      <c r="H34" s="6">
-        <v>2</v>
-      </c>
-      <c r="I34" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="B35" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="B36" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B37" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="C38" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="6" t="s">
+      <c r="K61" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26">
+      <c r="A62" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B39" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="B40" s="6">
+      <c r="B62" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26">
+      <c r="A63" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="B63" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B41" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="B42" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D43" s="6">
-        <v>3</v>
-      </c>
-      <c r="F43" s="6">
-        <v>1</v>
-      </c>
-      <c r="G43" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="B44" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="B45" s="6">
-        <v>1</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="C46" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="B47" s="6">
-        <v>1</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="B48" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:33">
-      <c r="A49" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="B49" s="6">
-        <v>10</v>
-      </c>
-      <c r="E49" s="6">
-        <v>1</v>
-      </c>
-      <c r="AG49" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:33">
-      <c r="A50" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D50" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF50" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:33">
-      <c r="A51" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="B51" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:33">
-      <c r="A52" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="B52" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:33">
-      <c r="A53" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B53" s="6">
-        <v>3</v>
-      </c>
-      <c r="C53" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:33">
-      <c r="A54" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="B54" s="6">
-        <v>4</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:33">
-      <c r="A55" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="B55" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:33">
-      <c r="A56" s="6" t="s">
+    <row r="64" spans="1:26">
+      <c r="A64" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D56" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:33">
-      <c r="A57" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="B57" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:33">
-      <c r="A58" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="B58" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:33">
-      <c r="A59" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E59" s="6">
-        <v>1</v>
-      </c>
-      <c r="J59" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:33">
-      <c r="A60" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="B60" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:33">
-      <c r="A61" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E61" s="6">
-        <v>4</v>
-      </c>
-      <c r="H61" s="6">
-        <v>1</v>
-      </c>
-      <c r="L61" s="6">
-        <v>1</v>
-      </c>
-      <c r="P61" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="6">
-        <v>1</v>
-      </c>
-      <c r="S61" s="6">
-        <v>1</v>
-      </c>
-      <c r="U61" s="6">
-        <v>1</v>
-      </c>
-      <c r="V61" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:33">
-      <c r="A62" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B62" s="6">
-        <v>1</v>
-      </c>
-      <c r="C62" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:33">
-      <c r="A63" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="B63" s="6">
-        <v>1</v>
-      </c>
-      <c r="C63" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:33">
-      <c r="A64" s="6" t="s">
+      <c r="D64" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:31">
+      <c r="A65" s="6" t="s">
         <v>466</v>
-      </c>
-      <c r="B64" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:34">
-      <c r="A65" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="B65" s="6">
         <v>2</v>
       </c>
-      <c r="C65" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:34">
+    </row>
+    <row r="66" spans="1:31">
       <c r="A66" s="6" t="s">
-        <v>524</v>
+        <v>470</v>
       </c>
       <c r="B66" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:31">
       <c r="A67" s="6" t="s">
-        <v>558</v>
+        <v>306</v>
       </c>
       <c r="B67" s="6">
+        <v>1</v>
+      </c>
+      <c r="C67" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:31">
+      <c r="A68" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D68" s="6">
         <v>2</v>
       </c>
-      <c r="K67" s="6">
-        <v>1</v>
-      </c>
-      <c r="AE67" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:34">
-      <c r="A68" s="6" t="s">
+      <c r="AA68" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:31">
+      <c r="A69" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D69" s="6">
+        <v>3</v>
+      </c>
+      <c r="F69" s="6">
+        <v>1</v>
+      </c>
+      <c r="G69" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:31">
+      <c r="A70" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="F70" s="6">
+        <v>1</v>
+      </c>
+      <c r="J70" s="6">
+        <v>1</v>
+      </c>
+      <c r="R70" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y70" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE70" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:31">
+      <c r="A71" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E68" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:34">
-      <c r="A69" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B69" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:34">
-      <c r="A70" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="B70" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:34">
-      <c r="A71" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="C71" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:34">
+      <c r="E71" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:31">
       <c r="A72" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E72" s="6">
+        <v>1</v>
+      </c>
+      <c r="J72" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:31">
+      <c r="A73" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K73" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:31">
+      <c r="A74" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="B74" s="6">
+        <v>11</v>
+      </c>
+      <c r="I74" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31">
+      <c r="A75" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B75" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:31">
+      <c r="A76" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B76" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:31">
+      <c r="A77" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F77" s="6">
+        <v>1</v>
+      </c>
+      <c r="G77" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:31">
+      <c r="A78" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F72" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:34">
-      <c r="A73" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="B73" s="6">
-        <v>1</v>
-      </c>
-      <c r="AH73" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:34">
-      <c r="A74" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="B74" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:34">
-      <c r="A75" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B75" s="6">
+      <c r="F78" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:31">
+      <c r="A79" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="C79" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:31">
+      <c r="A80" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E80" s="6">
         <v>4</v>
       </c>
-      <c r="C75" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:34">
-      <c r="A76" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F76" s="6">
-        <v>1</v>
-      </c>
-      <c r="H76" s="6">
-        <v>2</v>
-      </c>
-      <c r="I76" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:34">
-      <c r="A77" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="B77" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:34">
-      <c r="A78" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="O78" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB78" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:34">
-      <c r="A79" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="C79" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:34">
-      <c r="A80" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E80" s="6">
-        <v>1</v>
-      </c>
-      <c r="J80" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="H80" s="6">
+        <v>1</v>
+      </c>
+      <c r="L80" s="6">
+        <v>1</v>
+      </c>
+      <c r="O80" s="6">
+        <v>1</v>
+      </c>
+      <c r="P80" s="6">
+        <v>1</v>
+      </c>
+      <c r="S80" s="6">
+        <v>1</v>
+      </c>
+      <c r="T80" s="6">
+        <v>1</v>
+      </c>
+      <c r="V80" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="G81" s="6">
+        <v>482</v>
+      </c>
+      <c r="B81" s="6">
         <v>1</v>
       </c>
     </row>
@@ -17367,7 +17367,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C4" s="8">
         <v>1</v>
